--- a/task_2_1.xlsx
+++ b/task_2_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E612AF-B5A6-4BFB-92FA-FF38623786C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106D2165-0491-443D-8FFB-D7BB5E777D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BA488F58-8722-4F94-BC64-9EB65B0E8F44}"/>
   </bookViews>
@@ -68,311 +68,311 @@
     <t>Мэдлэг ойлголт</t>
   </si>
   <si>
-    <t>Процент гэдэг нь тоог хэдэн хэсэгт хуваасны нэг хэсэг вэ?A. 10 B. 100 C. 1000 D. 1</t>
-  </si>
-  <si>
-    <t>0.45-ыг процентоор илэрхийл.A. 4.5% B. 0.45% C. 45% D. 450%</t>
-  </si>
-  <si>
-    <t>1/5-ийг процентоор илэрхийл.A. 10% B. 20% C. 50% D. 5%</t>
-  </si>
-  <si>
-    <t>12.5%-ийг аравтын бутархайгаар илэрхийл.A. 1.25 B. 0.125 C. 0.0125 D. 12.5</t>
-  </si>
-  <si>
-    <t>80-ийн 20%-ийг ол.A. 16 B. 8 C. 4 D. 20</t>
-  </si>
-  <si>
-    <t>30% нь 15 байх тоог ол.A. 45 B. 30 C. 50 D. 150</t>
-  </si>
-  <si>
-    <t>2/3-ийг процентоор илэрхийл.A. 66% B. 66.6% C. 66.(6)% D. 67%</t>
-  </si>
-  <si>
-    <t>150-ийн 10% хэд вэ?A. 1.5 B. 15 C. 0.15 D. 150</t>
-  </si>
-  <si>
-    <t>Анги 30 сурагчтай, 12 нь охин бол охидын эзлэх хувийг ол.A. 30% B. 40% C. 12% D. 50%</t>
-  </si>
-  <si>
-    <t>400-ийн 1%-ийг ол.A. 40 B. 4 C. 0.4 D. 0.04</t>
-  </si>
-  <si>
-    <t>75%-ийг энгийн бутархайгаар илэрхийл.A. 1/4 B. 1/2 C. 3/4 D. 2/3</t>
-  </si>
-  <si>
-    <t>0.005-ыг процентоор илэрхийл.A. 0.5% B. 5% C. 50% D. 0.05%</t>
-  </si>
-  <si>
-    <t>250-ийн 40% хэд вэ?A. 10 B. 100 C. 40 D. 25</t>
-  </si>
-  <si>
-    <t>60% нь 120 байх тоог ол.A. 72 B. 180 C. 200 D. 300</t>
-  </si>
-  <si>
-    <t>5/8-ыг процентоор илэрхийл.A. 62.5% B. 58% C. 85% D. 60%</t>
-  </si>
-  <si>
-    <t>Хадгаламжийн хүүг юугаар хэмждэг вэ?A. Төгрөг B. Процент C. Хугацаа D. Масштаб</t>
-  </si>
-  <si>
-    <t>1000-ын 0.1% хэд вэ?A. 100 B. 10 C. 1 D. 0.1</t>
-  </si>
-  <si>
-    <t>3/10-ыг процентоор илэрхийл.A. 3% B. 13% C. 30% D. 0.3%</t>
-  </si>
-  <si>
-    <t>50-ийн 150% хэд вэ?A. 75 B. 100 C. 150 D. 50</t>
-  </si>
-  <si>
-    <t>8% нь 40 байх тоог ол.A. 500 B. 320 C. 400 D. 50</t>
-  </si>
-  <si>
-    <t>Хоёр тооны харьцааг юу гэж нэрлэдэг вэ?A. Пропорц B. Ногдвор C. Үржвэр D. Нийлбэр</t>
-  </si>
-  <si>
-    <t>18 охин, 6 хүүтэй ангийн охидын тоог хөвгүүдэд харьцуулсан харьцаа?A. 1:3 B. 3:1 C. 2:9 D. 9:2</t>
-  </si>
-  <si>
-    <t>12:4 харьцааг хялбарчил.A. 4:1 B. 3:1 C. 6:2 D. 12:4</t>
-  </si>
-  <si>
-    <t>Харьцааны гишүүн бүрийг тэгээс ялгаатай тоогоор үржүүлбэл харьцаа өөрчлөгдөх үү?A. Өөрчлөгдөнө B. Өөрчлөгдөхгүй C. Ихэснэ D. Багасна</t>
-  </si>
-  <si>
-    <t>200 г ба 1 кг-ын харьцааг ол.A. 200:1 B. 2:1 C. 1:5 D. 1:2</t>
-  </si>
-  <si>
-    <t>Хоёр харьцааны тэнцэтгэлийг юу гэх вэ?A. Харьцаа B. Пропорц C. Процент D. Тэгшитгэл</t>
-  </si>
-  <si>
-    <t>x:10 = 3:5 пропорцын x-ийг ол.A. 3 B. 5 C. 6 D. 15</t>
-  </si>
-  <si>
-    <t>Пропорцын захын гишүүдийн үржвэр юутай тэнцүү вэ?A. Дунд гишүүдийн үржвэр B. Захын гишүүдийн нийлбэр C. 1 D. 0</t>
-  </si>
-  <si>
-    <t>4:a = 8:2 бол a хэд вэ?A. 1 B. 2 C. 4 D. 16</t>
-  </si>
-  <si>
-    <t>Масштаб 1:100,000 бол газрын зураг дээрх 1 см бодит байдал дээр хэдэн км бэ?A. 1 км B. 10 км C. 100 км D. 0.1 км</t>
-  </si>
-  <si>
-    <t>3:4 ба 6:8 харьцаанууд пропорц үүсгэх үү?A. Үүсгэнэ B. Үүсгэхгүй C. Тэнцүү биш D. Тодорхойгүй</t>
-  </si>
-  <si>
-    <t>15:3 харьцааг 1:k хэлбэрт бич.A. 1:5 B. 1:0.2 C. 1:3 D. 1:15</t>
-  </si>
-  <si>
-    <t>Пропорцын мэдэгдэхгүй байгаа гишүүнийг олох үйлдлийг юу гэх вэ?A. Харьцаа B. Пропорц бодох C. Процентлох D. Хуваах</t>
-  </si>
-  <si>
-    <t>8:12 = 2:x бол x-ийг ол.A. 3 B. 4 C. 6 D. 24</t>
-  </si>
-  <si>
-    <t>Шууд пропорционал хамаарлын томьёо аль нь вэ?A. y = k/x B. y = kx C. y = x+k D. y = x-k</t>
-  </si>
-  <si>
-    <t>7:3 харьцааг 35:x болгож өргөтгөвөл x хэд вэ?A. 10 B. 15 C. 21 D. 14</t>
-  </si>
-  <si>
-    <t>120-ийг 2:3 харьцаагаар хуваахад бага хэсэг нь хэд вэ?A. 40 B. 48 C. 60 D. 80</t>
-  </si>
-  <si>
-    <t>Урвуу пропорционал хамаарлын томьёо аль нь вэ?A. y = kx B. y = k/x C. y = x^2 D. y = k+x</t>
-  </si>
-  <si>
-    <t>2:5 = x:25 бол x хэд вэ?A. 5 B. 10 C. 15 D. 2</t>
-  </si>
-  <si>
-    <t>Масштаб гэдэг нь юуны харьцаа вэ?A. Зургийн урт : Бодит урт B. Бодит урт : Зургийн урт C. Өргөн : Урт D. Хурд : Хугацаа</t>
-  </si>
-  <si>
-    <t>600-ийн 15% хэд вэ?A. 60 B. 90 C. 15 D. 100</t>
-  </si>
-  <si>
-    <t>Тоо 10%-иар өсвөл анхны тоо хэдэн хувь болох вэ?A. 10% B. 90% C. 110% D. 100%</t>
-  </si>
-  <si>
-    <t>Тоо 20%-иар буурвал анхны тоо хэдэн хувь болох вэ?A. 20% B. 80% C. 120% D. 100%</t>
-  </si>
-  <si>
-    <t>1200 төгрөгийн бараа 10% хямдарвал ямар үнэтэй болох вэ?A. 120₮ B. 1080₮ C. 1320₮ D. 1100₮</t>
-  </si>
-  <si>
-    <t>300-г 20%-иар ихэсгэвэл хэд болох вэ?A. 320 B. 360 C. 240 D. 60</t>
-  </si>
-  <si>
-    <t>Концентрац гэдэг нь юу вэ?A. Нийт масс B. Ууссан бодисын эзлэх хувь C. Усны хэмжээ D. Савны багтаамж</t>
-  </si>
-  <si>
-    <t>200 г уусмалд 10 г давс байвал концентрац хэд вэ?A. 10% B. 5% C. 20% D. 1%</t>
-  </si>
-  <si>
-    <t>Энгийн хүүгээр тооцохдоо хүүг юунаас боддог вэ?A. Өмнөх жилийн үлдэгдэл B. Анхны мөнгө C. Нийт мөнгө D. Зөвхөн хүү</t>
-  </si>
-  <si>
-    <t>Нийлмэл хүүгээр тооцохдоо хүүг юунаас боддог вэ?A. Анхны мөнгө B. Тухайн үеийн мөнгөн дүнгээс C. Хугацаанаас D. Масштабаас</t>
-  </si>
-  <si>
-    <t>НӨАТ (нэмэгдсэн өртгийн татвар) Монголд хэдэн хувь байдаг вэ?A. 5% B. 10% C. 15% D. 20%</t>
-  </si>
-  <si>
-    <t>20% нь 40 байх тоог ол.A. 80 B. 200 C. 400 D. 100</t>
-  </si>
-  <si>
-    <t>1/2-ийг процентоор илэрхийл.A. 50% B. 25% C. 100% D. 5%</t>
-  </si>
-  <si>
-    <t>3:x = 9:27 бол x хэд вэ?A. 3 B. 9 C. 12 D. 27</t>
-  </si>
-  <si>
-    <t>25%-ийг аравтын бутархайгаар бич.A. 2.5 B. 0.25 C. 0.025 D. 25</t>
-  </si>
-  <si>
-    <t>500₮-ийг 50%-иар бууруулбал?A. 250₮ B. 50₮ C. 450₮ D. 0₮</t>
-  </si>
-  <si>
-    <t>Тооны 1/4 хэсэг нь хэдэн хувь бэ?A. 10% B. 20% C. 25% D. 40%</t>
-  </si>
-  <si>
-    <t>80-ийн хэдэн хувь нь 20 бэ?A. 20% B. 25% C. 40% D. 80%</t>
-  </si>
-  <si>
-    <t>1:5 харьцааг процентоор илэрхийл.A. 10% B. 20% C. 5% D. 50%</t>
-  </si>
-  <si>
-    <t>Пропорц: 10/2 = x/5 бол x=?A. 25 B. 10 C. 20 D. 50</t>
-  </si>
-  <si>
-    <t>100%-ийг бүхэл тоогоор илэрхийл.A. 100 B. 10 C. 1 D. 0.1</t>
-  </si>
-  <si>
-    <t>5%-ийг аравтын бутархайгаар илэрхийл.A. 0.5 B. 0.05 C. 0.005 D. 5</t>
-  </si>
-  <si>
-    <t>300-ийн 3% хэд вэ?A. 3 B. 9 C. 30 D. 90</t>
-  </si>
-  <si>
-    <t>2:3 = 4:6 пропорц үнэн үү?A. Тийм B. Үгүй C. Мэдэхгүй D. Алдаатай</t>
-  </si>
-  <si>
-    <t>150-г 100% ихэсгэвэл хэд болох вэ?A. 150 B. 300 C. 250 D. 450</t>
-  </si>
-  <si>
-    <t>Тооны 10% нь 7 бол уг тоог ол.A. 0.7 B. 70 C. 700 D. 17</t>
-  </si>
-  <si>
-    <t>4:5 харьцааг процентоор илэрхийл.A. 40% B. 80% C. 90% D. 45%</t>
-  </si>
-  <si>
-    <t>1000₮-ийн 10%-ийн хөнгөлөлт хэдэн төгрөг вэ?A. 1₮ B. 10₮ C. 100₮ D. 900₮</t>
-  </si>
-  <si>
-    <t>0.125-ыг процентоор илэрхийл.A. 1.25% B. 12.5% C. 125% D. 0.125%</t>
-  </si>
-  <si>
-    <t>x:5 = 4:2 бол x=?A. 10 B. 2.5 C. 20 D. 1</t>
-  </si>
-  <si>
-    <t>Нийт 40 алимны 25% нь муудсан бол хэдэн алим муудсан бэ?A. 10 B. 5 C. 20 D. 25</t>
-  </si>
-  <si>
-    <t>2/5-ыг процентоор илэрхийл.A. 20% B. 40% C. 25% D. 50%</t>
-  </si>
-  <si>
-    <t>60-ын 120% хэд вэ?A. 60 B. 72 C. 120 D. 180</t>
-  </si>
-  <si>
-    <t>Тооны 50% нь 10 бол 100% нь хэд вэ?A. 5 B. 20 C. 50 D. 100</t>
-  </si>
-  <si>
-    <t>Масштаб 1:500 бол зураг дээрх 2 см бодит байдалд хэд вэ?A. 1000 см B. 250 см C. 502 см D. 10 м</t>
-  </si>
-  <si>
-    <t>Харьцаа a:b-д a-г юу гэж нэрлэдэг вэ?A. Өмнөх гишүүн B. Дараах гишүүн C. Дунд гишүүн D. Процент</t>
-  </si>
-  <si>
-    <t>Банканд 100,000₮ хадгалуулаад жилийн 10% хүү авбал хэд болох вэ?A. 110,000₮ B. 100,010₮ C. 10,000₮ D. 101,000₮</t>
-  </si>
-  <si>
-    <t>1/8 хэсэг нь хэдэн хувь бэ?A. 12% B. 12.5% C. 8% D. 80%</t>
-  </si>
-  <si>
-    <t>5:x = 1:2 бол x=?A. 2.5 B. 10 C. 5 D. 1</t>
-  </si>
-  <si>
-    <t>0.01-ийг процентоор илэрхийл.A. 10% B. 1% C. 0.1% D. 100%</t>
-  </si>
-  <si>
-    <t>400-ийн 25% хэд вэ?A. 4 B. 100 C. 40 D. 25</t>
-  </si>
-  <si>
-    <t>7:1 харьцааг 1:k хэлбэрт бич.A. 1:7 B. 1:0.14 C. 1:1 D. 1:0.7</t>
-  </si>
-  <si>
-    <t>Тооны 200% нь 50 бол уг тоог ол.A. 100 B. 25 C. 50 D. 150</t>
-  </si>
-  <si>
-    <t>Пропорц: a/b = c/d бол a*d = ?A. bc B. ac C. b*d D. 1</t>
-  </si>
-  <si>
-    <t>6/20 бутархайг процентоор илэрхийл.A. 6% B. 20% C. 30% D. 60%</t>
-  </si>
-  <si>
-    <t>Тоог 50% бууруулах нь хэдэд хуваасантай адил вэ?A. 50 B. 10 C. 2 D. 1</t>
-  </si>
-  <si>
-    <t>Масштаб 1:2 бол энэ нь ...A. Томруулсан B. Багасгасан C. Бодит хэмжээ D. Өнцөг</t>
-  </si>
-  <si>
-    <t>x:2 = 10:4 бол x=?A. 5 B. 1 C. 10 D. 20</t>
-  </si>
-  <si>
-    <t>40-ийн 5% хэд вэ?A. 2 B. 4 C. 20 D. 0.2</t>
-  </si>
-  <si>
-    <t>80% нь 64 байх тоог ол.A. 80 B. 100 C. 64 D. 128</t>
-  </si>
-  <si>
-    <t>1/10-ыг процентоор илэрхийл.A. 1% B. 10% C. 0.1% D. 100%</t>
-  </si>
-  <si>
-    <t>150 г уусмалын 10% нь давс бол хэдэн грамм давс байна вэ?A. 10 г B. 15 г C. 1.5 г D. 150 г</t>
-  </si>
-  <si>
-    <t>3:4 харьцааг 15:x болгож өргөтгөвөл x=?A. 16 B. 20 C. 12 D. 15</t>
-  </si>
-  <si>
-    <t>0.375-ыг процентоор илэрхийл.A. 3.75% B. 37.5% C. 375% D. 0.375%</t>
-  </si>
-  <si>
-    <t>Пропорцын захын гишүүд 2 ба 10, нэг дунд гишүүн 4 бол нөгөөг ол.A. 5 B. 8 C. 20 D. 1</t>
-  </si>
-  <si>
-    <t>1000-ын 150% хэд вэ?A. 150 B. 1500 C. 1000 D. 15</t>
-  </si>
-  <si>
-    <t>Тоог 100% ихэсгэх нь хэдээр үржүүлсэнтй адил вэ?A. 1 B. 2 C. 100 D. 0</t>
-  </si>
-  <si>
-    <t>6:8 = 3:4 пропорц үнэн үү?A. Тийм B. Үгүй C. Харьцаа биш D. Тодорхойгүй</t>
-  </si>
-  <si>
-    <t>200-ийн 0.5% хэд вэ?A. 100 B. 10 C. 1 D. 0.1</t>
-  </si>
-  <si>
-    <t>90% нь 81 байх тоог ол.A. 9 B. 90 C. 100 D. 81</t>
-  </si>
-  <si>
-    <t>Тооны 1/20 хэсэг нь хэдэн хувь бэ?A. 1% B. 5% C. 20% D. 10%</t>
+    <t>Процент гэдэг нь тоог хэдэн хэсэгт хуваасны нэг хэсэг вэ? 1A. $10$ B. $100$ C. $1000$ D. $1$</t>
+  </si>
+  <si>
+    <t>$0.45$-ыг процентоор илэрхийл. 2A. $4.5\%$ B. $0.45\%$ C. $45\%$ D. $450\%$</t>
+  </si>
+  <si>
+    <t>$1/5$-ийг процентоор илэрхийл. 1A. $10\%$ B. $20\%$ C. $50\%$ D. $5\%$</t>
+  </si>
+  <si>
+    <t>$12.5\%$-ийг аравтын бутархайгаар илэрхийл. 2A. $1.25$ B. $0.125$ C. $0.0125$ D. $12.5$</t>
+  </si>
+  <si>
+    <t>$80$-ийн $20\%$-ийг ол. 3A. $16$ B. $8$ C. $4$ D. $20$</t>
+  </si>
+  <si>
+    <t>$30\%$ нь $15$ байх тоог ол. 3A. $45$ B. $30$ C. $50$ D. $150$</t>
+  </si>
+  <si>
+    <t>$2/3$-ийг процентоор илэрхийл. 1A. $66\%$ B. $66.6\%$ C. $66.(6)\%$ D. $67\%$</t>
+  </si>
+  <si>
+    <t>$150$-ийн $10\%$ хэд вэ? 3A. $1.5$ B. $15$ C. $0.15$ D. $150$</t>
+  </si>
+  <si>
+    <t>Анги $30$ сурагчтай, $12$ нь охин бол охидын эзлэх хувийг ол. 1A. $30\%$ B. $40\%$ C. $12\%$ D. $50\%$</t>
+  </si>
+  <si>
+    <t>$400$-ийн $1\%$-ийг ол. 1A. $40$ B. $4$ C. $0.4$ D. $0.04$</t>
+  </si>
+  <si>
+    <t>$75\%$-ийг энгийн бутархайгаар илэрхийл. 3A. $1/4$ B. $1/2$ C. $3/4$ D. $2/3$</t>
+  </si>
+  <si>
+    <t>$0.005$-ыг процентоор илэрхийл. 2A. $0.5\%$ B. $5\%$ C. $50\%$ D. $0.05\%$</t>
+  </si>
+  <si>
+    <t>$250$-ийн $40\%$ хэд вэ? 3A. $10$ B. $100$ C. $40$ D. $25$</t>
+  </si>
+  <si>
+    <t>$60\%$ нь $120$ байх тоог ол. 3A. $72$ B. $180$ C. $200$ D. $300$</t>
+  </si>
+  <si>
+    <t>$5/8$-ыг процентоор илэрхийл. 1A. $62.5\%$ B. $58\%$ C. $85\%$ D. $60\%$</t>
+  </si>
+  <si>
+    <t>Хадгаламжийн хүүг юугаар хэмждэг вэ? 4A. Төгрөг B. Процент C. Хугацаа D. Масштаб</t>
+  </si>
+  <si>
+    <t>$1000$-ын $0.1\%$ хэд вэ? 2A. $100$ B. $10$ C. $1$ D. $0.1$</t>
+  </si>
+  <si>
+    <t>$3/10$-ыг процентоор илэрхийл. 1A. $3\%$ B. $13\%$ C. $30\%$ D. $0.3\%$</t>
+  </si>
+  <si>
+    <t>$50$-ийн $150\%$ хэд вэ? 5A. $75$ B. $100$ C. $150$ D. $50$</t>
+  </si>
+  <si>
+    <t>$8\%$ нь $40$ байх тоог ол. 3A. $500$ B. $320$ C. $400$ D. $50$</t>
+  </si>
+  <si>
+    <t>Хоёр тооны харьцааг юу гэж нэрлэдэг вэ? 6A. Пропорц B. Ногдвор C. Үржвэр D. Нийлбэр</t>
+  </si>
+  <si>
+    <t>$18$ охин, $6$ хүүтэй ангийн охидын тоог хөвгүүдэд харьцуулсан харьцаа? 7A. $1:3$ B. $3:1$ C. $2:9$ D. $9:2$</t>
+  </si>
+  <si>
+    <t>$12:4$ харьцааг хялбарчил. 8A. $4:1$ B. $3:1$ C. $6:2$ D. $12:4$</t>
+  </si>
+  <si>
+    <t>Харьцааны гишүүн бүрийг тэгээс ялгаатай тоогоор үржүүлбэл харьцаа өөрчлөгдөх үү? 6A. Өөрчлөгдөнө B. Өөрчлөгдөхгүй C. Ихэснэ D. Багасна</t>
+  </si>
+  <si>
+    <t>$200$ г ба $1$ кг-ын харьцааг ол. 6A. $200:1$ B. $2:1$ C. $1:5$ D. $1:2$</t>
+  </si>
+  <si>
+    <t>Хоёр харьцааны тэнцэтгэлийг юу гэх вэ? 6A. Харьцаа B. Пропорц C. Процент D. Тэгшитгэл</t>
+  </si>
+  <si>
+    <t>$x:10 = 3:5$ пропорцын $x$-ийг ол. 8A. $3$ B. $5$ C. $6$ D. $15$</t>
+  </si>
+  <si>
+    <t>Пропорцын захын гишүүдийн үржвэр юутай тэнцүү вэ? 8A. Дунд гишүүдийн үржвэр B. Захын гишүүдийн нийлбэр C. $1$ D. $0$</t>
+  </si>
+  <si>
+    <t>$4:a = 8:2$ бол $a$ хэд вэ? 8A. $1$ B. $2$ C. $4$ D. $16$</t>
+  </si>
+  <si>
+    <t>Масштаб $1:100,000$ бол газрын зураг дээрх $1$ см бодит байдал дээр хэдэн км бэ? 9A. $1$ км B. $10$ км C. $100$ км D. $0.1$ км</t>
+  </si>
+  <si>
+    <t>$3:4$ ба $6:8$ харьцаанууд пропорц үүсгэх үү? 8A. Үүсгэнэ B. Үүсгэхгүй C. Тэнцүү биш D. Тодорхойгүй</t>
+  </si>
+  <si>
+    <t>$15:3$ харьцааг $1:k$ хэлбэрт бич. 6A. $1:5$ B. $1:0.2$ C. $1:3$ D. $1:15$</t>
+  </si>
+  <si>
+    <t>Пропорцын мэдэгдэхгүй байгаа гишүүнийг олох үйлдлийг юу гэх вэ? 8A. Харьцаа B. Пропорц бодох C. Процентлох D. Хуваах</t>
+  </si>
+  <si>
+    <t>$8:12 = 2:x$ бол $x$-ийг ол. 8A. $3$ B. $4$ C. $6$ D. $24$</t>
+  </si>
+  <si>
+    <t>Шууд пропорционал хамаарлын томьёо аль нь вэ? 10A. $y = k/x$ B. $y = kx$ C. $y = x+k$ D. $y = x-k$</t>
+  </si>
+  <si>
+    <t>$7:3$ харьцааг $35:x$ болгож өргөтгөвөл $x$ хэд вэ? 6A. $10$ B. $15$ C. $21$ D. $14$</t>
+  </si>
+  <si>
+    <t>$120$-ийг $2:3$ харьцаагаар хуваахад бага хэсэг нь хэд вэ? 8A. $40$ B. $48$ C. $60$ D. $80$</t>
+  </si>
+  <si>
+    <t>Урвуу пропорционал хамаарлын томьёо аль нь вэ? 11A. $y = kx$ B. $y = k/x$ C. $y = x^2$ D. $y = k+x$</t>
+  </si>
+  <si>
+    <t>$2:5 = x:25$ бол $x$ хэд вэ? 8A. $5$ B. $10$ C. $15$ D. $2$</t>
+  </si>
+  <si>
+    <t>Масштаб гэдэг нь юуны харьцаа вэ? 11A. Зургийн урт : Бодит урт B. Бодит урт : Зургийн урт C. Өргөн : Урт D. Хурд : Хугацаа</t>
+  </si>
+  <si>
+    <t>$600$-ийн $15\%$ хэд вэ? 3A. $60$ B. $90$ C. $15$ D. $100$</t>
+  </si>
+  <si>
+    <t>Тоо $10\%$-иар өсвөл анхны тоо хэдэн хувь болох вэ? 5A. $10\%$ B. $90\%$ C. $110\%$ D. $100\%$</t>
+  </si>
+  <si>
+    <t>Тоо $20\%$-иар буурвал анхны тоо хэдэн хувь болох вэ? 5A. $20\%$ B. $80\%$ C. $120\%$ D. $100\%$</t>
+  </si>
+  <si>
+    <t>$1200$ төгрөгийн бараа $10\%$ хямдарвал ямар үнэтэй болох вэ? 12A. $120$ ₮ B. $1080$ ₮ C. $1320$ ₮ D. $1100$ ₮</t>
+  </si>
+  <si>
+    <t>$300$-г $20\%$-иар ихэсгэвэл хэд болох вэ? 13A. $320$ B. $360$ C. $240$ D. $60$</t>
+  </si>
+  <si>
+    <t>Концентрац гэдэг нь юу вэ? 14A. Нийт масс B. Ууссан бодисын эзлэх хувь C. Усны хэмжээ D. Савны багтаамж</t>
+  </si>
+  <si>
+    <t>$200$ г уусмалд $10$ г давс байвал концентрац хэд вэ? 14A. $10\%$ B. $5\%$ C. $20\%$ D. $1\%$</t>
+  </si>
+  <si>
+    <t>Энгийн хүүгээр тооцохдоо хүүг юунаас боддог вэ? 14A. Өмнөх жилийн үлдэгдэл B. Анхны мөнгө C. Нийт мөнгө D. Зөвхөн хүү</t>
+  </si>
+  <si>
+    <t>Нийлмэл хүүгээр тооцохдоо хүүг юунаас боддог вэ? 4A. Анхны мөнгө B. Тухайн үеийн мөнгөн дүнгээс C. Хугацаанаас D. Масштабаас</t>
+  </si>
+  <si>
+    <t>НӨАТ (нэмэгдсэн өртгийн татвар) Монголд хэдэн хувь байдаг вэ? 15A. $5\%$ B. $10\%$ C. $15\%$ D. $20\%$</t>
+  </si>
+  <si>
+    <t>$20\%$ нь $40$ байх тоог ол. 3A. $80$ B. $200$ C. $400$ D. $100$</t>
+  </si>
+  <si>
+    <t>$1/2$-ийг процентоор илэрхийл. 16A. $50\%$ B. $25\%$ C. $100\%$ D. $5\%$</t>
+  </si>
+  <si>
+    <t>$3:x = 9:27$ бол $x$ хэд вэ? 8A. $3$ B. $9$ C. $12$ D. $27$</t>
+  </si>
+  <si>
+    <t>$25\%$-ийг аравтын бутархайгаар бич. 2A. $2.5$ B. $0.25$ C. $0.025$ D. $25$</t>
+  </si>
+  <si>
+    <t>$500$ ₮-ийг $50\%$-иар бууруулбал? 13A. $250$ ₮ B. $50$ ₮ C. $450$ ₮ D. $0$ ₮</t>
+  </si>
+  <si>
+    <t>Тооны $1/4$ хэсэг нь хэдэн хувь бэ? 16A. $10\%$ B. $20\%$ C. $25\%$ D. $40\%$</t>
+  </si>
+  <si>
+    <t>$80$-ийн хэдэн хувь нь $20$ бэ? 3A. $20\%$ B. $25\%$ C. $40\%$ D. $80\%$</t>
+  </si>
+  <si>
+    <t>$1:5$ харьцааг процентоор илэрхийл. 1A. $10\%$ B. $20\%$ C. $5\%$ D. $50\%$</t>
+  </si>
+  <si>
+    <t>Пропорц: $10/2 = x/5$ бол $x=$? 8A. $25$ B. $10$ C. $20$ D. $50$</t>
+  </si>
+  <si>
+    <t>$100\%$-ийг бүхэл тоогоор илэрхийл. 3A. $100$ B. $10$ C. $1$ D. $0.1$</t>
+  </si>
+  <si>
+    <t>$5\%$-ийг аравтын бутархайгаар илэрхийл. 2A. $0.5$ B. $0.05$ C. $0.005$ D. $5$</t>
+  </si>
+  <si>
+    <t>$300$-ийн $3\%$ хэд вэ? 3A. $3$ B. $9$ C. $30$ D. $90$</t>
+  </si>
+  <si>
+    <t>$2:3 = 4:6$ пропорц үнэн үү? 8A. Тийм B. Үгүй C. Мэдэхгүй D. Алдаатай</t>
+  </si>
+  <si>
+    <t>$150$-г $100\%$ ихэсгэвэл хэд болох вэ? 13A. $150$ B. $300$ C. $250$ D. $450$</t>
+  </si>
+  <si>
+    <t>Тооны $10\%$ нь $7$ бол уг тоог ол. 3A. $0.7$ B. $70$ C. $700$ D. $17$</t>
+  </si>
+  <si>
+    <t>$4:5$ харьцааг процентоор илэрхийл. 7A. $40\%$ B. $80\%$ C. $90\%$ D. $45\%$</t>
+  </si>
+  <si>
+    <t>$1000$ ₮-ийн $10\%$-ийн хөнгөлөлт хэдэн төгрөг вэ? 12A. $1$ ₮ B. $10$ ₮ C. $100$ ₮ D. $900$ ₮</t>
+  </si>
+  <si>
+    <t>$0.125$-ыг процентоор илэрхийл. 1A. $1.25\%$ B. $12.5\%$ C. $125\%$ D. $0.125\%$</t>
+  </si>
+  <si>
+    <t>$x:5 = 4:2$ бол $x=$? 8A. $10$ B. $2.5$ C. $20$ D. $1$</t>
+  </si>
+  <si>
+    <t>Нийт $40$ алимны $25\%$ нь муудсан бол хэдэн алим муудсан бэ? 3A. $10$ B. $5$ C. $20$ D. $25$</t>
+  </si>
+  <si>
+    <t>$2/5$-ыг процентоор илэрхийл. 16A. $20\%$ B. $40\%$ C. $25\%$ D. $50\%$</t>
+  </si>
+  <si>
+    <t>$60$-ын $120\%$ хэд вэ? 5A. $60$ B. $72$ C. $120$ D. $180$</t>
+  </si>
+  <si>
+    <t>Тооны $50\%$ нь $10$ бол $100\%$ нь хэд вэ? 3A. $5$ B. $20$ C. $50$ D. $100$</t>
+  </si>
+  <si>
+    <t>Масштаб $1:500$ бол зураг дээрх $2$ см бодит байдалд хэд вэ? 17A. $1000$ см B. $250$ см C. $502$ см D. $10$ м</t>
+  </si>
+  <si>
+    <t>Харьцаа $a:b$-д $a$-г юу гэж нэрлэдэг вэ? 6A. Өмнөх гишүүн B. Дараах гишүүн C. Дунд гишүүн D. Процент</t>
+  </si>
+  <si>
+    <t>Банканд $100,000$ ₮ хадгалуулаад жилийн $10\%$ хүү авбал хэд болох вэ? 14A. $110,000$ ₮ B. $100,010$ ₮ C. $10,000$ ₮ D. $101,000$ ₮</t>
+  </si>
+  <si>
+    <t>$1/8$ хэсэг нь хэдэн хувь бэ? 1A. $12\%$ B. $12.5\%$ C. $8\%$ D. $80\%$</t>
+  </si>
+  <si>
+    <t>$5:x = 1:2$ бол $x=$? 8A. $2.5$ B. $10$ C. $5$ D. $1$</t>
+  </si>
+  <si>
+    <t>$0.01$-ийг процентоор илэрхийл. 1A. $10\%$ B. $1\%$ C. $0.1\%$ D. $100\%$</t>
+  </si>
+  <si>
+    <t>$400$-ийн $25\%$ хэд вэ? 3A. $4$ B. $100$ C. $40$ D. $25$</t>
+  </si>
+  <si>
+    <t>$7:1$ харьцааг $1:k$ хэлбэрт бич. 18A. $1:7$ B. $1:0.14$ C. $1:1$ D. $1:0.7$</t>
+  </si>
+  <si>
+    <t>Тооны $200\%$ нь $50$ бол уг тоог ол. 13A. $100$ B. $25$ C. $50$ D. $150$</t>
+  </si>
+  <si>
+    <t>Пропорц: $a/b = c/d$ бол $a \cdot d = ?$ 8A. $b \cdot c$ B. $a \cdot c$ C. $b \cdot d$ D. $1$</t>
+  </si>
+  <si>
+    <t>$6/20$ бутархайг процентоор илэрхийл. 1A. $6\%$ B. $20\%$ C. $30\%$ D. $60\%$</t>
+  </si>
+  <si>
+    <t>Тоог $50\%$ бууруулах нь хэдэд хуваасантай адил вэ? 3A. $50$ B. $10$ C. $2$ D. $1$</t>
+  </si>
+  <si>
+    <t>Масштаб $1:2$ бол энэ нь ... 11A. Томруулсан B. Багасгасан C. Бодит хэмжээ D. Өнцөг</t>
+  </si>
+  <si>
+    <t>$x:2 = 10:4$ бол $x=$? 8A. $5$ B. $1$ C. $10$ D. $20$</t>
+  </si>
+  <si>
+    <t>$40$-ийн $5\%$ хэд вэ? 3A. $2$ B. $4$ C. $20$ D. $0.2$</t>
+  </si>
+  <si>
+    <t>$80\%$ нь $64$ байх тоог ол. 3A. $80$ B. $100$ C. $64$ D. $128$</t>
+  </si>
+  <si>
+    <t>$1/10$-ыг процентоор илэрхийл. 1A. $1\%$ B. $10\%$ C. $0.1\%$ D. $100\%$</t>
+  </si>
+  <si>
+    <t>$150$ г уусмалын $10\%$ нь давс бол хэдэн грамм давс байна вэ? 14A. $10$ г B. $15$ г C. $1.5$ г D. $150$ г</t>
+  </si>
+  <si>
+    <t>$3:4$ харьцааг $15:x$ болгож өргөтгөвөл $x=$? 6A. $16$ B. $20$ C. $12$ D. $15$</t>
+  </si>
+  <si>
+    <t>$0.375$-ыг процентоор илэрхийл. 1A. $3.75\%$ B. $37.5\%$ C. $375\%$ D. $0.375\%$</t>
+  </si>
+  <si>
+    <t>Пропорцын захын гишүүд $2$ ба $10$, нэг дунд гишүүн $4$ бол нөгөөг ол. 8A. $5$ B. $8$ C. $20$ D. $1$</t>
+  </si>
+  <si>
+    <t>$1000$-ын $150\%$ хэд вэ? 5A. $150$ B. $1500$ C. $1000$ D. $15$</t>
+  </si>
+  <si>
+    <t>Тоог $100\%$ ихэсгэх нь хэдээр үржүүлсэнтэй адил вэ? 13A. $1$ B. $2$ C. $100$ D. $0$</t>
+  </si>
+  <si>
+    <t>$6:8 = 3:4$ пропорц үнэн үү? 8A. Тийм B. Үгүй C. Харьцаа биш D. Тодорхойгүй</t>
+  </si>
+  <si>
+    <t>$200$-ийн $0.5\%$ хэд вэ? 2A. $100$ B. $10$ C. $1$ D. $0.1$</t>
+  </si>
+  <si>
+    <t>$90\%$ нь $81$ байх тоог ол. 3A. $9$ B. $90$ C. $100$ D. $81$</t>
+  </si>
+  <si>
+    <t>Тооны $1/20$ хэсэг нь хэдэн хувь бэ? 16A. $1\%$ B. $5\%$ C. $20\%$ D. $10\%$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,13 +386,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -447,22 +440,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1047,7 +1040,7 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="116.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1065,10 +1058,10 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1079,10 +1072,10 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1093,10 +1086,10 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1107,10 +1100,10 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1121,10 +1114,10 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1135,10 +1128,10 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1149,10 +1142,10 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1163,10 +1156,10 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1177,10 +1170,10 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1191,10 +1184,10 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1205,10 +1198,10 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1219,10 +1212,10 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1233,10 +1226,10 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1247,10 +1240,10 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -1261,10 +1254,10 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -1275,10 +1268,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -1289,10 +1282,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1303,10 +1296,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1317,10 +1310,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -1331,10 +1324,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1345,10 +1338,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -1359,10 +1352,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -1373,10 +1366,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -1387,10 +1380,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -1401,10 +1394,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1415,10 +1408,10 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -1429,10 +1422,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -1443,10 +1436,10 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -1457,10 +1450,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -1471,10 +1464,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -1485,10 +1478,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -1499,10 +1492,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -1513,10 +1506,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -1527,10 +1520,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -1541,10 +1534,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -1555,10 +1548,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -1569,10 +1562,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -1583,10 +1576,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -1597,10 +1590,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -1611,10 +1604,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -1625,10 +1618,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -1639,10 +1632,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -1653,10 +1646,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -1667,10 +1660,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -1681,10 +1674,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -1695,10 +1688,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -1709,10 +1702,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -1723,10 +1716,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -1737,10 +1730,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -1751,10 +1744,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -1765,10 +1758,10 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -1779,10 +1772,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -1793,10 +1786,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -1807,10 +1800,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -1821,10 +1814,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -1835,10 +1828,10 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -1849,10 +1842,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -1863,10 +1856,10 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -1877,10 +1870,10 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -1891,10 +1884,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
@@ -1905,10 +1898,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -1919,10 +1912,10 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -1933,10 +1926,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -1947,10 +1940,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -1961,10 +1954,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -1975,10 +1968,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -1989,10 +1982,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -2003,10 +1996,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -2017,10 +2010,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -2031,10 +2024,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -2045,10 +2038,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C72" s="2" t="s">
@@ -2059,10 +2052,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C73" s="2" t="s">
@@ -2073,10 +2066,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -2087,10 +2080,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
@@ -2101,10 +2094,10 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -2115,10 +2108,10 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
@@ -2129,10 +2122,10 @@
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C78" s="2" t="s">
@@ -2143,10 +2136,10 @@
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="2" t="s">
@@ -2157,10 +2150,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -2171,10 +2164,10 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C81" s="2" t="s">
@@ -2185,10 +2178,10 @@
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
@@ -2199,10 +2192,10 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C83" s="2" t="s">
@@ -2213,10 +2206,10 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
@@ -2227,10 +2220,10 @@
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
@@ -2241,10 +2234,10 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
@@ -2255,10 +2248,10 @@
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C87" s="2" t="s">
@@ -2269,10 +2262,10 @@
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
@@ -2283,10 +2276,10 @@
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
@@ -2297,10 +2290,10 @@
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -2311,10 +2304,10 @@
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C91" s="2" t="s">
@@ -2325,10 +2318,10 @@
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C92" s="2" t="s">
@@ -2339,10 +2332,10 @@
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C93" s="2" t="s">
@@ -2353,10 +2346,10 @@
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -2367,10 +2360,10 @@
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
@@ -2381,10 +2374,10 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C96" s="2" t="s">
@@ -2395,10 +2388,10 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C97" s="2" t="s">
@@ -2409,10 +2402,10 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
@@ -2423,10 +2416,10 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
@@ -2437,10 +2430,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C100" s="2" t="s">
@@ -2451,10 +2444,10 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C101" s="2" t="s">
@@ -2465,2706 +2458,2706 @@
       </c>
     </row>
     <row r="102" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-      <c r="B102" s="5"/>
+      <c r="A102" s="5"/>
+      <c r="B102" s="4"/>
     </row>
     <row r="103" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-      <c r="B103" s="5"/>
+      <c r="A103" s="5"/>
+      <c r="B103" s="4"/>
     </row>
     <row r="104" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="5"/>
+      <c r="A104" s="5"/>
+      <c r="B104" s="4"/>
     </row>
     <row r="105" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="8"/>
-      <c r="B105" s="5"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="4"/>
     </row>
     <row r="106" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="5"/>
+      <c r="A106" s="5"/>
+      <c r="B106" s="4"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B107" s="5"/>
+      <c r="B107" s="4"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B108" s="5"/>
+      <c r="B108" s="4"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B109" s="5"/>
+      <c r="B109" s="4"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B110" s="5"/>
+      <c r="B110" s="4"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B111" s="5"/>
+      <c r="B111" s="4"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B112" s="5"/>
+      <c r="B112" s="4"/>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B113" s="5"/>
+      <c r="B113" s="4"/>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B114" s="5"/>
+      <c r="B114" s="4"/>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B115" s="5"/>
+      <c r="B115" s="4"/>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B116" s="5"/>
+      <c r="B116" s="4"/>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B117" s="5"/>
+      <c r="B117" s="4"/>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B118" s="5"/>
+      <c r="B118" s="4"/>
     </row>
     <row r="119" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B119" s="5"/>
+      <c r="B119" s="4"/>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B120" s="5"/>
+      <c r="B120" s="4"/>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B121" s="5"/>
+      <c r="B121" s="4"/>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B122" s="5"/>
+      <c r="B122" s="4"/>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B123" s="5"/>
+      <c r="B123" s="4"/>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B124" s="5"/>
+      <c r="B124" s="4"/>
     </row>
     <row r="125" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B125" s="5"/>
+      <c r="B125" s="4"/>
     </row>
     <row r="126" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B126" s="5"/>
+      <c r="B126" s="4"/>
     </row>
     <row r="127" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B127" s="5"/>
+      <c r="B127" s="4"/>
     </row>
     <row r="128" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B128" s="5"/>
+      <c r="B128" s="4"/>
     </row>
     <row r="129" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B129" s="5"/>
+      <c r="B129" s="4"/>
     </row>
     <row r="130" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B130" s="5"/>
+      <c r="B130" s="4"/>
     </row>
     <row r="131" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B131" s="5"/>
+      <c r="B131" s="4"/>
     </row>
     <row r="132" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B132" s="5"/>
+      <c r="B132" s="4"/>
     </row>
     <row r="133" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B133" s="5"/>
+      <c r="B133" s="4"/>
     </row>
     <row r="134" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B134" s="5"/>
+      <c r="B134" s="4"/>
     </row>
     <row r="135" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B135" s="5"/>
+      <c r="B135" s="4"/>
     </row>
     <row r="136" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B136" s="5"/>
+      <c r="B136" s="4"/>
     </row>
     <row r="137" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B137" s="5"/>
+      <c r="B137" s="4"/>
     </row>
     <row r="138" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B138" s="5"/>
+      <c r="B138" s="4"/>
     </row>
     <row r="139" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B139" s="5"/>
+      <c r="B139" s="4"/>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B140" s="5"/>
+      <c r="B140" s="4"/>
     </row>
     <row r="141" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B141" s="5"/>
+      <c r="B141" s="4"/>
     </row>
     <row r="142" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B142" s="5"/>
+      <c r="B142" s="4"/>
     </row>
     <row r="143" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B143" s="5"/>
+      <c r="B143" s="4"/>
     </row>
     <row r="144" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B144" s="5"/>
+      <c r="B144" s="4"/>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B145" s="5"/>
+      <c r="B145" s="4"/>
     </row>
     <row r="146" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B146" s="5"/>
+      <c r="B146" s="4"/>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B147" s="5"/>
+      <c r="B147" s="4"/>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B148" s="5"/>
+      <c r="B148" s="4"/>
     </row>
     <row r="149" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B149" s="5"/>
+      <c r="B149" s="4"/>
     </row>
     <row r="150" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B150" s="5"/>
+      <c r="B150" s="4"/>
     </row>
     <row r="151" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B151" s="5"/>
+      <c r="B151" s="4"/>
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B152" s="5"/>
+      <c r="B152" s="4"/>
     </row>
     <row r="153" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B153" s="5"/>
+      <c r="B153" s="4"/>
     </row>
     <row r="154" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B154" s="5"/>
+      <c r="B154" s="4"/>
     </row>
     <row r="155" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B155" s="5"/>
+      <c r="B155" s="4"/>
     </row>
     <row r="156" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B156" s="5"/>
+      <c r="B156" s="4"/>
     </row>
     <row r="157" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B157" s="5"/>
+      <c r="B157" s="4"/>
     </row>
     <row r="158" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B158" s="5"/>
+      <c r="B158" s="4"/>
     </row>
     <row r="159" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B159" s="5"/>
+      <c r="B159" s="4"/>
     </row>
     <row r="160" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B160" s="5"/>
+      <c r="B160" s="4"/>
     </row>
     <row r="161" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B161" s="5"/>
+      <c r="B161" s="4"/>
     </row>
     <row r="162" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B162" s="5"/>
+      <c r="B162" s="4"/>
     </row>
     <row r="163" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B163" s="5"/>
+      <c r="B163" s="4"/>
     </row>
     <row r="164" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B164" s="5"/>
+      <c r="B164" s="4"/>
     </row>
     <row r="165" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B165" s="5"/>
+      <c r="B165" s="4"/>
     </row>
     <row r="166" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B166" s="5"/>
+      <c r="B166" s="4"/>
     </row>
     <row r="167" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B167" s="5"/>
+      <c r="B167" s="4"/>
     </row>
     <row r="168" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B168" s="5"/>
+      <c r="B168" s="4"/>
     </row>
     <row r="169" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B169" s="5"/>
+      <c r="B169" s="4"/>
     </row>
     <row r="170" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B170" s="5"/>
+      <c r="B170" s="4"/>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B171" s="5"/>
+      <c r="B171" s="4"/>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B172" s="5"/>
+      <c r="B172" s="4"/>
     </row>
     <row r="173" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B173" s="5"/>
+      <c r="B173" s="4"/>
     </row>
     <row r="174" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B174" s="5"/>
+      <c r="B174" s="4"/>
     </row>
     <row r="175" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B175" s="5"/>
+      <c r="B175" s="4"/>
     </row>
     <row r="176" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B176" s="5"/>
+      <c r="B176" s="4"/>
     </row>
     <row r="177" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B177" s="5"/>
+      <c r="B177" s="4"/>
     </row>
     <row r="178" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B178" s="5"/>
+      <c r="B178" s="4"/>
     </row>
     <row r="179" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B179" s="5"/>
+      <c r="B179" s="4"/>
     </row>
     <row r="180" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B180" s="5"/>
+      <c r="B180" s="4"/>
     </row>
     <row r="181" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B181" s="5"/>
+      <c r="B181" s="4"/>
     </row>
     <row r="182" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B182" s="5"/>
+      <c r="B182" s="4"/>
     </row>
     <row r="183" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B183" s="5"/>
+      <c r="B183" s="4"/>
     </row>
     <row r="184" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B184" s="5"/>
+      <c r="B184" s="4"/>
     </row>
     <row r="185" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B185" s="5"/>
+      <c r="B185" s="4"/>
     </row>
     <row r="186" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B186" s="5"/>
+      <c r="B186" s="4"/>
     </row>
     <row r="187" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B187" s="5"/>
+      <c r="B187" s="4"/>
     </row>
     <row r="188" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B188" s="5"/>
+      <c r="B188" s="4"/>
     </row>
     <row r="189" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B189" s="5"/>
+      <c r="B189" s="4"/>
     </row>
     <row r="190" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B190" s="5"/>
+      <c r="B190" s="4"/>
     </row>
     <row r="191" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B191" s="5"/>
+      <c r="B191" s="4"/>
     </row>
     <row r="192" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B192" s="5"/>
+      <c r="B192" s="4"/>
     </row>
     <row r="193" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B193" s="5"/>
+      <c r="B193" s="4"/>
     </row>
     <row r="194" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B194" s="5"/>
+      <c r="B194" s="4"/>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B195" s="5"/>
+      <c r="B195" s="4"/>
     </row>
     <row r="196" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B196" s="5"/>
+      <c r="B196" s="4"/>
     </row>
     <row r="197" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B197" s="5"/>
+      <c r="B197" s="4"/>
     </row>
     <row r="198" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B198" s="5"/>
+      <c r="B198" s="4"/>
     </row>
     <row r="199" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B199" s="5"/>
+      <c r="B199" s="4"/>
     </row>
     <row r="200" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B200" s="5"/>
+      <c r="B200" s="4"/>
     </row>
     <row r="201" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B201" s="5"/>
+      <c r="B201" s="4"/>
     </row>
     <row r="202" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B202" s="5"/>
+      <c r="B202" s="4"/>
     </row>
     <row r="203" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B203" s="5"/>
+      <c r="B203" s="4"/>
     </row>
     <row r="204" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B204" s="5"/>
+      <c r="B204" s="4"/>
     </row>
     <row r="205" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B205" s="5"/>
+      <c r="B205" s="4"/>
     </row>
     <row r="206" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B206" s="5"/>
+      <c r="B206" s="4"/>
     </row>
     <row r="207" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B207" s="5"/>
+      <c r="B207" s="4"/>
     </row>
     <row r="208" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B208" s="5"/>
+      <c r="B208" s="4"/>
     </row>
     <row r="209" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B209" s="5"/>
+      <c r="B209" s="4"/>
     </row>
     <row r="210" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B210" s="5"/>
+      <c r="B210" s="4"/>
     </row>
     <row r="211" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B211" s="5"/>
+      <c r="B211" s="4"/>
     </row>
     <row r="212" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B212" s="5"/>
+      <c r="B212" s="4"/>
     </row>
     <row r="213" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B213" s="5"/>
+      <c r="B213" s="4"/>
     </row>
     <row r="214" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B214" s="5"/>
+      <c r="B214" s="4"/>
     </row>
     <row r="215" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B215" s="5"/>
+      <c r="B215" s="4"/>
     </row>
     <row r="216" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B216" s="5"/>
+      <c r="B216" s="4"/>
     </row>
     <row r="217" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B217" s="5"/>
+      <c r="B217" s="4"/>
     </row>
     <row r="218" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B218" s="5"/>
+      <c r="B218" s="4"/>
     </row>
     <row r="219" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B219" s="5"/>
+      <c r="B219" s="4"/>
     </row>
     <row r="220" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B220" s="5"/>
+      <c r="B220" s="4"/>
     </row>
     <row r="221" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B221" s="5"/>
+      <c r="B221" s="4"/>
     </row>
     <row r="222" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B222" s="5"/>
+      <c r="B222" s="4"/>
     </row>
     <row r="223" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B223" s="5"/>
+      <c r="B223" s="4"/>
     </row>
     <row r="224" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B224" s="5"/>
+      <c r="B224" s="4"/>
     </row>
     <row r="225" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B225" s="5"/>
+      <c r="B225" s="4"/>
     </row>
     <row r="226" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B226" s="5"/>
+      <c r="B226" s="4"/>
     </row>
     <row r="227" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B227" s="5"/>
+      <c r="B227" s="4"/>
     </row>
     <row r="228" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B228" s="5"/>
+      <c r="B228" s="4"/>
     </row>
     <row r="229" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B229" s="5"/>
+      <c r="B229" s="4"/>
     </row>
     <row r="230" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B230" s="5"/>
+      <c r="B230" s="4"/>
     </row>
     <row r="231" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B231" s="5"/>
+      <c r="B231" s="4"/>
     </row>
     <row r="232" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B232" s="5"/>
+      <c r="B232" s="4"/>
     </row>
     <row r="233" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B233" s="5"/>
+      <c r="B233" s="4"/>
     </row>
     <row r="234" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B234" s="5"/>
+      <c r="B234" s="4"/>
     </row>
     <row r="235" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B235" s="5"/>
+      <c r="B235" s="4"/>
     </row>
     <row r="236" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B236" s="5"/>
+      <c r="B236" s="4"/>
     </row>
     <row r="237" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B237" s="5"/>
+      <c r="B237" s="4"/>
     </row>
     <row r="238" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B238" s="5"/>
+      <c r="B238" s="4"/>
     </row>
     <row r="239" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B239" s="5"/>
+      <c r="B239" s="4"/>
     </row>
     <row r="240" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B240" s="5"/>
+      <c r="B240" s="4"/>
     </row>
     <row r="241" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B241" s="5"/>
+      <c r="B241" s="4"/>
     </row>
     <row r="242" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B242" s="5"/>
+      <c r="B242" s="4"/>
     </row>
     <row r="243" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B243" s="5"/>
+      <c r="B243" s="4"/>
     </row>
     <row r="244" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B244" s="5"/>
+      <c r="B244" s="4"/>
     </row>
     <row r="245" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B245" s="5"/>
+      <c r="B245" s="4"/>
     </row>
     <row r="246" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B246" s="5"/>
+      <c r="B246" s="4"/>
     </row>
     <row r="247" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B247" s="5"/>
+      <c r="B247" s="4"/>
     </row>
     <row r="248" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B248" s="5"/>
+      <c r="B248" s="4"/>
     </row>
     <row r="249" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B249" s="5"/>
+      <c r="B249" s="4"/>
     </row>
     <row r="250" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B250" s="5"/>
+      <c r="B250" s="4"/>
     </row>
     <row r="251" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B251" s="5"/>
+      <c r="B251" s="4"/>
     </row>
     <row r="252" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B252" s="5"/>
+      <c r="B252" s="4"/>
     </row>
     <row r="253" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B253" s="5"/>
+      <c r="B253" s="4"/>
     </row>
     <row r="254" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B254" s="5"/>
+      <c r="B254" s="4"/>
     </row>
     <row r="255" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B255" s="5"/>
+      <c r="B255" s="4"/>
     </row>
     <row r="256" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B256" s="5"/>
+      <c r="B256" s="4"/>
     </row>
     <row r="257" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B257" s="5"/>
+      <c r="B257" s="4"/>
     </row>
     <row r="258" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B258" s="5"/>
+      <c r="B258" s="4"/>
     </row>
     <row r="259" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B259" s="5"/>
+      <c r="B259" s="4"/>
     </row>
     <row r="260" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B260" s="5"/>
+      <c r="B260" s="4"/>
     </row>
     <row r="261" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B261" s="5"/>
+      <c r="B261" s="4"/>
     </row>
     <row r="262" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B262" s="5"/>
+      <c r="B262" s="4"/>
     </row>
     <row r="263" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B263" s="5"/>
+      <c r="B263" s="4"/>
     </row>
     <row r="264" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B264" s="5"/>
+      <c r="B264" s="4"/>
     </row>
     <row r="265" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B265" s="5"/>
+      <c r="B265" s="4"/>
     </row>
     <row r="266" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B266" s="5"/>
+      <c r="B266" s="4"/>
     </row>
     <row r="267" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B267" s="5"/>
+      <c r="B267" s="4"/>
     </row>
     <row r="268" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B268" s="5"/>
+      <c r="B268" s="4"/>
     </row>
     <row r="269" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B269" s="5"/>
+      <c r="B269" s="4"/>
     </row>
     <row r="270" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B270" s="5"/>
+      <c r="B270" s="4"/>
     </row>
     <row r="271" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B271" s="5"/>
+      <c r="B271" s="4"/>
     </row>
     <row r="272" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B272" s="5"/>
+      <c r="B272" s="4"/>
     </row>
     <row r="273" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B273" s="5"/>
+      <c r="B273" s="4"/>
     </row>
     <row r="274" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B274" s="5"/>
+      <c r="B274" s="4"/>
     </row>
     <row r="275" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B275" s="5"/>
+      <c r="B275" s="4"/>
     </row>
     <row r="276" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B276" s="5"/>
+      <c r="B276" s="4"/>
     </row>
     <row r="277" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B277" s="5"/>
+      <c r="B277" s="4"/>
     </row>
     <row r="278" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B278" s="5"/>
+      <c r="B278" s="4"/>
     </row>
     <row r="279" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B279" s="5"/>
+      <c r="B279" s="4"/>
     </row>
     <row r="280" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B280" s="5"/>
+      <c r="B280" s="4"/>
     </row>
     <row r="281" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B281" s="5"/>
+      <c r="B281" s="4"/>
     </row>
     <row r="282" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B282" s="5"/>
+      <c r="B282" s="4"/>
     </row>
     <row r="283" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B283" s="5"/>
+      <c r="B283" s="4"/>
     </row>
     <row r="284" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B284" s="5"/>
+      <c r="B284" s="4"/>
     </row>
     <row r="285" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B285" s="5"/>
+      <c r="B285" s="4"/>
     </row>
     <row r="286" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B286" s="5"/>
+      <c r="B286" s="4"/>
     </row>
     <row r="287" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B287" s="5"/>
+      <c r="B287" s="4"/>
     </row>
     <row r="288" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B288" s="5"/>
+      <c r="B288" s="4"/>
     </row>
     <row r="289" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B289" s="5"/>
+      <c r="B289" s="4"/>
     </row>
     <row r="290" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B290" s="5"/>
+      <c r="B290" s="4"/>
     </row>
     <row r="291" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B291" s="5"/>
+      <c r="B291" s="4"/>
     </row>
     <row r="292" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B292" s="5"/>
+      <c r="B292" s="4"/>
     </row>
     <row r="293" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B293" s="5"/>
+      <c r="B293" s="4"/>
     </row>
     <row r="294" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B294" s="5"/>
+      <c r="B294" s="4"/>
     </row>
     <row r="295" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B295" s="5"/>
+      <c r="B295" s="4"/>
     </row>
     <row r="296" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B296" s="5"/>
+      <c r="B296" s="4"/>
     </row>
     <row r="297" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B297" s="5"/>
+      <c r="B297" s="4"/>
     </row>
     <row r="298" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B298" s="5"/>
+      <c r="B298" s="4"/>
     </row>
     <row r="299" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B299" s="5"/>
+      <c r="B299" s="4"/>
     </row>
     <row r="300" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B300" s="5"/>
+      <c r="B300" s="4"/>
     </row>
     <row r="301" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B301" s="5"/>
+      <c r="B301" s="4"/>
     </row>
     <row r="302" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B302" s="5"/>
+      <c r="B302" s="4"/>
     </row>
     <row r="303" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B303" s="5"/>
+      <c r="B303" s="4"/>
     </row>
     <row r="304" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B304" s="5"/>
+      <c r="B304" s="4"/>
     </row>
     <row r="305" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B305" s="5"/>
+      <c r="B305" s="4"/>
     </row>
     <row r="306" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B306" s="5"/>
+      <c r="B306" s="4"/>
     </row>
     <row r="307" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B307" s="5"/>
+      <c r="B307" s="4"/>
     </row>
     <row r="308" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B308" s="5"/>
+      <c r="B308" s="4"/>
     </row>
     <row r="309" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B309" s="5"/>
+      <c r="B309" s="4"/>
     </row>
     <row r="310" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B310" s="5"/>
+      <c r="B310" s="4"/>
     </row>
     <row r="311" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B311" s="5"/>
+      <c r="B311" s="4"/>
     </row>
     <row r="312" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B312" s="5"/>
+      <c r="B312" s="4"/>
     </row>
     <row r="313" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B313" s="5"/>
+      <c r="B313" s="4"/>
     </row>
     <row r="314" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B314" s="5"/>
+      <c r="B314" s="4"/>
     </row>
     <row r="315" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B315" s="5"/>
+      <c r="B315" s="4"/>
     </row>
     <row r="316" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B316" s="5"/>
+      <c r="B316" s="4"/>
     </row>
     <row r="317" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B317" s="5"/>
+      <c r="B317" s="4"/>
     </row>
     <row r="318" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B318" s="5"/>
+      <c r="B318" s="4"/>
     </row>
     <row r="319" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B319" s="5"/>
+      <c r="B319" s="4"/>
     </row>
     <row r="320" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B320" s="5"/>
+      <c r="B320" s="4"/>
     </row>
     <row r="321" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B321" s="5"/>
+      <c r="B321" s="4"/>
     </row>
     <row r="322" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B322" s="5"/>
+      <c r="B322" s="4"/>
     </row>
     <row r="323" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B323" s="5"/>
+      <c r="B323" s="4"/>
     </row>
     <row r="324" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B324" s="5"/>
+      <c r="B324" s="4"/>
     </row>
     <row r="325" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B325" s="5"/>
+      <c r="B325" s="4"/>
     </row>
     <row r="326" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B326" s="5"/>
+      <c r="B326" s="4"/>
     </row>
     <row r="327" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B327" s="5"/>
+      <c r="B327" s="4"/>
     </row>
     <row r="328" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B328" s="5"/>
+      <c r="B328" s="4"/>
     </row>
     <row r="329" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B329" s="5"/>
+      <c r="B329" s="4"/>
     </row>
     <row r="330" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B330" s="5"/>
+      <c r="B330" s="4"/>
     </row>
     <row r="331" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B331" s="5"/>
+      <c r="B331" s="4"/>
     </row>
     <row r="332" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B332" s="5"/>
+      <c r="B332" s="4"/>
     </row>
     <row r="333" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B333" s="5"/>
+      <c r="B333" s="4"/>
     </row>
     <row r="334" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B334" s="5"/>
+      <c r="B334" s="4"/>
     </row>
     <row r="335" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B335" s="5"/>
+      <c r="B335" s="4"/>
     </row>
     <row r="336" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B336" s="5"/>
+      <c r="B336" s="4"/>
     </row>
     <row r="337" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B337" s="5"/>
+      <c r="B337" s="4"/>
     </row>
     <row r="338" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B338" s="5"/>
+      <c r="B338" s="4"/>
     </row>
     <row r="339" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B339" s="5"/>
+      <c r="B339" s="4"/>
     </row>
     <row r="340" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B340" s="5"/>
+      <c r="B340" s="4"/>
     </row>
     <row r="341" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B341" s="5"/>
+      <c r="B341" s="4"/>
     </row>
     <row r="342" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B342" s="5"/>
+      <c r="B342" s="4"/>
     </row>
     <row r="343" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B343" s="5"/>
+      <c r="B343" s="4"/>
     </row>
     <row r="344" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B344" s="5"/>
+      <c r="B344" s="4"/>
     </row>
     <row r="345" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B345" s="5"/>
+      <c r="B345" s="4"/>
     </row>
     <row r="346" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B346" s="5"/>
+      <c r="B346" s="4"/>
     </row>
     <row r="347" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B347" s="5"/>
+      <c r="B347" s="4"/>
     </row>
     <row r="348" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B348" s="5"/>
+      <c r="B348" s="4"/>
     </row>
     <row r="349" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B349" s="5"/>
+      <c r="B349" s="4"/>
     </row>
     <row r="350" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B350" s="5"/>
+      <c r="B350" s="4"/>
     </row>
     <row r="351" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B351" s="5"/>
+      <c r="B351" s="4"/>
     </row>
     <row r="352" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B352" s="5"/>
+      <c r="B352" s="4"/>
     </row>
     <row r="353" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B353" s="5"/>
+      <c r="B353" s="4"/>
     </row>
     <row r="354" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B354" s="5"/>
+      <c r="B354" s="4"/>
     </row>
     <row r="355" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B355" s="5"/>
+      <c r="B355" s="4"/>
     </row>
     <row r="356" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B356" s="5"/>
+      <c r="B356" s="4"/>
     </row>
     <row r="357" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B357" s="5"/>
+      <c r="B357" s="4"/>
     </row>
     <row r="358" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B358" s="5"/>
+      <c r="B358" s="4"/>
     </row>
     <row r="359" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B359" s="5"/>
+      <c r="B359" s="4"/>
     </row>
     <row r="360" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B360" s="5"/>
+      <c r="B360" s="4"/>
     </row>
     <row r="361" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B361" s="5"/>
+      <c r="B361" s="4"/>
     </row>
     <row r="362" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B362" s="5"/>
+      <c r="B362" s="4"/>
     </row>
     <row r="363" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B363" s="5"/>
+      <c r="B363" s="4"/>
     </row>
     <row r="364" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B364" s="5"/>
+      <c r="B364" s="4"/>
     </row>
     <row r="365" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B365" s="5"/>
+      <c r="B365" s="4"/>
     </row>
     <row r="366" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B366" s="5"/>
+      <c r="B366" s="4"/>
     </row>
     <row r="367" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B367" s="5"/>
+      <c r="B367" s="4"/>
     </row>
     <row r="368" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B368" s="5"/>
+      <c r="B368" s="4"/>
     </row>
     <row r="369" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B369" s="5"/>
+      <c r="B369" s="4"/>
     </row>
     <row r="370" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B370" s="5"/>
+      <c r="B370" s="4"/>
     </row>
     <row r="371" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B371" s="5"/>
+      <c r="B371" s="4"/>
     </row>
     <row r="372" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B372" s="5"/>
+      <c r="B372" s="4"/>
     </row>
     <row r="373" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B373" s="5"/>
+      <c r="B373" s="4"/>
     </row>
     <row r="374" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B374" s="5"/>
+      <c r="B374" s="4"/>
     </row>
     <row r="375" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B375" s="5"/>
+      <c r="B375" s="4"/>
     </row>
     <row r="376" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B376" s="5"/>
+      <c r="B376" s="4"/>
     </row>
     <row r="377" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B377" s="5"/>
+      <c r="B377" s="4"/>
     </row>
     <row r="378" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B378" s="5"/>
+      <c r="B378" s="4"/>
     </row>
     <row r="379" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B379" s="5"/>
+      <c r="B379" s="4"/>
     </row>
     <row r="380" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B380" s="5"/>
+      <c r="B380" s="4"/>
     </row>
     <row r="381" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B381" s="5"/>
+      <c r="B381" s="4"/>
     </row>
     <row r="382" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B382" s="5"/>
+      <c r="B382" s="4"/>
     </row>
     <row r="383" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B383" s="5"/>
+      <c r="B383" s="4"/>
     </row>
     <row r="384" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B384" s="5"/>
+      <c r="B384" s="4"/>
     </row>
     <row r="385" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B385" s="5"/>
+      <c r="B385" s="4"/>
     </row>
     <row r="386" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B386" s="5"/>
+      <c r="B386" s="4"/>
     </row>
     <row r="387" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B387" s="5"/>
+      <c r="B387" s="4"/>
     </row>
     <row r="388" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B388" s="5"/>
+      <c r="B388" s="4"/>
     </row>
     <row r="389" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B389" s="5"/>
+      <c r="B389" s="4"/>
     </row>
     <row r="390" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B390" s="5"/>
+      <c r="B390" s="4"/>
     </row>
     <row r="391" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B391" s="5"/>
+      <c r="B391" s="4"/>
     </row>
     <row r="392" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B392" s="5"/>
+      <c r="B392" s="4"/>
     </row>
     <row r="393" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B393" s="5"/>
+      <c r="B393" s="4"/>
     </row>
     <row r="394" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B394" s="5"/>
+      <c r="B394" s="4"/>
     </row>
     <row r="395" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B395" s="5"/>
+      <c r="B395" s="4"/>
     </row>
     <row r="396" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B396" s="5"/>
+      <c r="B396" s="4"/>
     </row>
     <row r="397" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B397" s="5"/>
+      <c r="B397" s="4"/>
     </row>
     <row r="398" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B398" s="5"/>
+      <c r="B398" s="4"/>
     </row>
     <row r="399" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B399" s="5"/>
+      <c r="B399" s="4"/>
     </row>
     <row r="400" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B400" s="5"/>
+      <c r="B400" s="4"/>
     </row>
     <row r="401" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B401" s="5"/>
+      <c r="B401" s="4"/>
     </row>
     <row r="402" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B402" s="5"/>
+      <c r="B402" s="4"/>
     </row>
     <row r="403" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B403" s="5"/>
+      <c r="B403" s="4"/>
     </row>
     <row r="404" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B404" s="5"/>
+      <c r="B404" s="4"/>
     </row>
     <row r="405" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B405" s="5"/>
+      <c r="B405" s="4"/>
     </row>
     <row r="406" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B406" s="5"/>
+      <c r="B406" s="4"/>
     </row>
     <row r="407" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B407" s="5"/>
+      <c r="B407" s="4"/>
     </row>
     <row r="408" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B408" s="5"/>
+      <c r="B408" s="4"/>
     </row>
     <row r="409" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B409" s="5"/>
+      <c r="B409" s="4"/>
     </row>
     <row r="410" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B410" s="5"/>
+      <c r="B410" s="4"/>
     </row>
     <row r="411" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B411" s="5"/>
+      <c r="B411" s="4"/>
     </row>
     <row r="412" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B412" s="5"/>
+      <c r="B412" s="4"/>
     </row>
     <row r="413" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B413" s="5"/>
+      <c r="B413" s="4"/>
     </row>
     <row r="414" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B414" s="5"/>
+      <c r="B414" s="4"/>
     </row>
     <row r="415" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B415" s="5"/>
+      <c r="B415" s="4"/>
     </row>
     <row r="416" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B416" s="5"/>
+      <c r="B416" s="4"/>
     </row>
     <row r="417" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B417" s="5"/>
+      <c r="B417" s="4"/>
     </row>
     <row r="418" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B418" s="5"/>
+      <c r="B418" s="4"/>
     </row>
     <row r="419" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B419" s="5"/>
+      <c r="B419" s="4"/>
     </row>
     <row r="420" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B420" s="5"/>
+      <c r="B420" s="4"/>
     </row>
     <row r="421" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B421" s="5"/>
+      <c r="B421" s="4"/>
     </row>
     <row r="422" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B422" s="5"/>
+      <c r="B422" s="4"/>
     </row>
     <row r="423" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B423" s="5"/>
+      <c r="B423" s="4"/>
     </row>
     <row r="424" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B424" s="5"/>
+      <c r="B424" s="4"/>
     </row>
     <row r="425" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B425" s="5"/>
+      <c r="B425" s="4"/>
     </row>
     <row r="426" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B426" s="5"/>
+      <c r="B426" s="4"/>
     </row>
     <row r="427" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B427" s="5"/>
+      <c r="B427" s="4"/>
     </row>
     <row r="428" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B428" s="5"/>
+      <c r="B428" s="4"/>
     </row>
     <row r="429" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B429" s="5"/>
+      <c r="B429" s="4"/>
     </row>
     <row r="430" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B430" s="5"/>
+      <c r="B430" s="4"/>
     </row>
     <row r="431" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B431" s="5"/>
+      <c r="B431" s="4"/>
     </row>
     <row r="432" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B432" s="5"/>
+      <c r="B432" s="4"/>
     </row>
     <row r="433" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B433" s="5"/>
+      <c r="B433" s="4"/>
     </row>
     <row r="434" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B434" s="5"/>
+      <c r="B434" s="4"/>
     </row>
     <row r="435" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B435" s="5"/>
+      <c r="B435" s="4"/>
     </row>
     <row r="436" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B436" s="5"/>
+      <c r="B436" s="4"/>
     </row>
     <row r="437" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B437" s="5"/>
+      <c r="B437" s="4"/>
     </row>
     <row r="438" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B438" s="5"/>
+      <c r="B438" s="4"/>
     </row>
     <row r="439" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B439" s="5"/>
+      <c r="B439" s="4"/>
     </row>
     <row r="440" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B440" s="5"/>
+      <c r="B440" s="4"/>
     </row>
     <row r="441" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B441" s="5"/>
+      <c r="B441" s="4"/>
     </row>
     <row r="442" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B442" s="5"/>
+      <c r="B442" s="4"/>
     </row>
     <row r="443" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B443" s="5"/>
+      <c r="B443" s="4"/>
     </row>
     <row r="444" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B444" s="5"/>
+      <c r="B444" s="4"/>
     </row>
     <row r="445" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B445" s="5"/>
+      <c r="B445" s="4"/>
     </row>
     <row r="446" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B446" s="5"/>
+      <c r="B446" s="4"/>
     </row>
     <row r="447" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B447" s="5"/>
+      <c r="B447" s="4"/>
     </row>
     <row r="448" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B448" s="5"/>
+      <c r="B448" s="4"/>
     </row>
     <row r="449" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B449" s="5"/>
+      <c r="B449" s="4"/>
     </row>
     <row r="450" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B450" s="5"/>
+      <c r="B450" s="4"/>
     </row>
     <row r="451" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B451" s="5"/>
+      <c r="B451" s="4"/>
     </row>
     <row r="452" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B452" s="5"/>
+      <c r="B452" s="4"/>
     </row>
     <row r="453" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B453" s="5"/>
+      <c r="B453" s="4"/>
     </row>
     <row r="454" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B454" s="5"/>
+      <c r="B454" s="4"/>
     </row>
     <row r="455" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B455" s="5"/>
+      <c r="B455" s="4"/>
     </row>
     <row r="456" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B456" s="5"/>
+      <c r="B456" s="4"/>
     </row>
     <row r="457" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B457" s="5"/>
+      <c r="B457" s="4"/>
     </row>
     <row r="458" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B458" s="5"/>
+      <c r="B458" s="4"/>
     </row>
     <row r="459" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B459" s="5"/>
+      <c r="B459" s="4"/>
     </row>
     <row r="460" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B460" s="5"/>
+      <c r="B460" s="4"/>
     </row>
     <row r="461" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B461" s="5"/>
+      <c r="B461" s="4"/>
     </row>
     <row r="462" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B462" s="5"/>
+      <c r="B462" s="4"/>
     </row>
     <row r="463" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B463" s="5"/>
+      <c r="B463" s="4"/>
     </row>
     <row r="464" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B464" s="5"/>
+      <c r="B464" s="4"/>
     </row>
     <row r="465" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B465" s="5"/>
+      <c r="B465" s="4"/>
     </row>
     <row r="466" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B466" s="5"/>
+      <c r="B466" s="4"/>
     </row>
     <row r="467" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B467" s="5"/>
+      <c r="B467" s="4"/>
     </row>
     <row r="468" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B468" s="5"/>
+      <c r="B468" s="4"/>
     </row>
     <row r="469" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B469" s="5"/>
+      <c r="B469" s="4"/>
     </row>
     <row r="470" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B470" s="5"/>
+      <c r="B470" s="4"/>
     </row>
     <row r="471" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B471" s="5"/>
+      <c r="B471" s="4"/>
     </row>
     <row r="472" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B472" s="5"/>
+      <c r="B472" s="4"/>
     </row>
     <row r="473" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B473" s="5"/>
+      <c r="B473" s="4"/>
     </row>
     <row r="474" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B474" s="5"/>
+      <c r="B474" s="4"/>
     </row>
     <row r="475" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B475" s="5"/>
+      <c r="B475" s="4"/>
     </row>
     <row r="476" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B476" s="5"/>
+      <c r="B476" s="4"/>
     </row>
     <row r="477" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B477" s="5"/>
+      <c r="B477" s="4"/>
     </row>
     <row r="478" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B478" s="5"/>
+      <c r="B478" s="4"/>
     </row>
     <row r="479" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B479" s="5"/>
+      <c r="B479" s="4"/>
     </row>
     <row r="480" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B480" s="5"/>
+      <c r="B480" s="4"/>
     </row>
     <row r="481" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B481" s="5"/>
+      <c r="B481" s="4"/>
     </row>
     <row r="482" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B482" s="5"/>
+      <c r="B482" s="4"/>
     </row>
     <row r="483" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B483" s="5"/>
+      <c r="B483" s="4"/>
     </row>
     <row r="484" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B484" s="5"/>
+      <c r="B484" s="4"/>
     </row>
     <row r="485" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B485" s="5"/>
+      <c r="B485" s="4"/>
     </row>
     <row r="486" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B486" s="5"/>
+      <c r="B486" s="4"/>
     </row>
     <row r="487" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B487" s="5"/>
+      <c r="B487" s="4"/>
     </row>
     <row r="488" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B488" s="5"/>
+      <c r="B488" s="4"/>
     </row>
     <row r="489" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B489" s="5"/>
+      <c r="B489" s="4"/>
     </row>
     <row r="490" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B490" s="5"/>
+      <c r="B490" s="4"/>
     </row>
     <row r="491" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B491" s="5"/>
+      <c r="B491" s="4"/>
     </row>
     <row r="492" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B492" s="5"/>
+      <c r="B492" s="4"/>
     </row>
     <row r="493" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B493" s="5"/>
+      <c r="B493" s="4"/>
     </row>
     <row r="494" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B494" s="5"/>
+      <c r="B494" s="4"/>
     </row>
     <row r="495" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B495" s="5"/>
+      <c r="B495" s="4"/>
     </row>
     <row r="496" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B496" s="5"/>
+      <c r="B496" s="4"/>
     </row>
     <row r="497" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B497" s="5"/>
+      <c r="B497" s="4"/>
     </row>
     <row r="498" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B498" s="5"/>
+      <c r="B498" s="4"/>
     </row>
     <row r="499" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B499" s="5"/>
+      <c r="B499" s="4"/>
     </row>
     <row r="500" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B500" s="5"/>
+      <c r="B500" s="4"/>
     </row>
     <row r="501" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B501" s="5"/>
+      <c r="B501" s="4"/>
     </row>
     <row r="502" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B502" s="5"/>
+      <c r="B502" s="4"/>
     </row>
     <row r="503" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B503" s="5"/>
+      <c r="B503" s="4"/>
     </row>
     <row r="504" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B504" s="5"/>
+      <c r="B504" s="4"/>
     </row>
     <row r="505" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B505" s="5"/>
+      <c r="B505" s="4"/>
     </row>
     <row r="506" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B506" s="5"/>
+      <c r="B506" s="4"/>
     </row>
     <row r="507" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B507" s="5"/>
+      <c r="B507" s="4"/>
     </row>
     <row r="508" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B508" s="5"/>
+      <c r="B508" s="4"/>
     </row>
     <row r="509" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B509" s="5"/>
+      <c r="B509" s="4"/>
     </row>
     <row r="510" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B510" s="5"/>
+      <c r="B510" s="4"/>
     </row>
     <row r="511" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B511" s="5"/>
+      <c r="B511" s="4"/>
     </row>
     <row r="512" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B512" s="5"/>
+      <c r="B512" s="4"/>
     </row>
     <row r="513" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B513" s="5"/>
+      <c r="B513" s="4"/>
     </row>
     <row r="514" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B514" s="5"/>
+      <c r="B514" s="4"/>
     </row>
     <row r="515" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B515" s="5"/>
+      <c r="B515" s="4"/>
     </row>
     <row r="516" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B516" s="5"/>
+      <c r="B516" s="4"/>
     </row>
     <row r="517" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B517" s="5"/>
+      <c r="B517" s="4"/>
     </row>
     <row r="518" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B518" s="5"/>
+      <c r="B518" s="4"/>
     </row>
     <row r="519" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B519" s="5"/>
+      <c r="B519" s="4"/>
     </row>
     <row r="520" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B520" s="5"/>
+      <c r="B520" s="4"/>
     </row>
     <row r="521" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B521" s="5"/>
+      <c r="B521" s="4"/>
     </row>
     <row r="522" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B522" s="5"/>
+      <c r="B522" s="4"/>
     </row>
     <row r="523" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B523" s="5"/>
+      <c r="B523" s="4"/>
     </row>
     <row r="524" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B524" s="5"/>
+      <c r="B524" s="4"/>
     </row>
     <row r="525" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B525" s="5"/>
+      <c r="B525" s="4"/>
     </row>
     <row r="526" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B526" s="5"/>
+      <c r="B526" s="4"/>
     </row>
     <row r="527" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B527" s="5"/>
+      <c r="B527" s="4"/>
     </row>
     <row r="528" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B528" s="5"/>
+      <c r="B528" s="4"/>
     </row>
     <row r="529" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B529" s="5"/>
+      <c r="B529" s="4"/>
     </row>
     <row r="530" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B530" s="5"/>
+      <c r="B530" s="4"/>
     </row>
     <row r="531" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B531" s="5"/>
+      <c r="B531" s="4"/>
     </row>
     <row r="532" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B532" s="5"/>
+      <c r="B532" s="4"/>
     </row>
     <row r="533" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B533" s="5"/>
+      <c r="B533" s="4"/>
     </row>
     <row r="534" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B534" s="5"/>
+      <c r="B534" s="4"/>
     </row>
     <row r="535" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B535" s="5"/>
+      <c r="B535" s="4"/>
     </row>
     <row r="536" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B536" s="5"/>
+      <c r="B536" s="4"/>
     </row>
     <row r="537" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B537" s="5"/>
+      <c r="B537" s="4"/>
     </row>
     <row r="538" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B538" s="5"/>
+      <c r="B538" s="4"/>
     </row>
     <row r="539" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B539" s="5"/>
+      <c r="B539" s="4"/>
     </row>
     <row r="540" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B540" s="5"/>
+      <c r="B540" s="4"/>
     </row>
     <row r="541" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B541" s="5"/>
+      <c r="B541" s="4"/>
     </row>
     <row r="542" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B542" s="5"/>
+      <c r="B542" s="4"/>
     </row>
     <row r="543" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B543" s="5"/>
+      <c r="B543" s="4"/>
     </row>
     <row r="544" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B544" s="5"/>
+      <c r="B544" s="4"/>
     </row>
     <row r="545" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B545" s="5"/>
+      <c r="B545" s="4"/>
     </row>
     <row r="546" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B546" s="5"/>
+      <c r="B546" s="4"/>
     </row>
     <row r="547" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B547" s="5"/>
+      <c r="B547" s="4"/>
     </row>
     <row r="548" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B548" s="5"/>
+      <c r="B548" s="4"/>
     </row>
     <row r="549" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B549" s="5"/>
+      <c r="B549" s="4"/>
     </row>
     <row r="550" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B550" s="5"/>
+      <c r="B550" s="4"/>
     </row>
     <row r="551" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B551" s="5"/>
+      <c r="B551" s="4"/>
     </row>
     <row r="552" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B552" s="5"/>
+      <c r="B552" s="4"/>
     </row>
     <row r="553" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B553" s="5"/>
+      <c r="B553" s="4"/>
     </row>
     <row r="554" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B554" s="5"/>
+      <c r="B554" s="4"/>
     </row>
     <row r="555" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B555" s="5"/>
+      <c r="B555" s="4"/>
     </row>
     <row r="556" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B556" s="5"/>
+      <c r="B556" s="4"/>
     </row>
     <row r="557" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B557" s="5"/>
+      <c r="B557" s="4"/>
     </row>
     <row r="558" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B558" s="5"/>
+      <c r="B558" s="4"/>
     </row>
     <row r="559" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B559" s="5"/>
+      <c r="B559" s="4"/>
     </row>
     <row r="560" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B560" s="5"/>
+      <c r="B560" s="4"/>
     </row>
     <row r="561" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B561" s="5"/>
+      <c r="B561" s="4"/>
     </row>
     <row r="562" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B562" s="5"/>
+      <c r="B562" s="4"/>
     </row>
     <row r="563" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B563" s="5"/>
+      <c r="B563" s="4"/>
     </row>
     <row r="564" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B564" s="5"/>
+      <c r="B564" s="4"/>
     </row>
     <row r="565" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B565" s="5"/>
+      <c r="B565" s="4"/>
     </row>
     <row r="566" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B566" s="5"/>
+      <c r="B566" s="4"/>
     </row>
     <row r="567" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B567" s="5"/>
+      <c r="B567" s="4"/>
     </row>
     <row r="568" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B568" s="5"/>
+      <c r="B568" s="4"/>
     </row>
     <row r="569" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B569" s="5"/>
+      <c r="B569" s="4"/>
     </row>
     <row r="570" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B570" s="5"/>
+      <c r="B570" s="4"/>
     </row>
     <row r="571" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B571" s="5"/>
+      <c r="B571" s="4"/>
     </row>
     <row r="572" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B572" s="5"/>
+      <c r="B572" s="4"/>
     </row>
     <row r="573" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B573" s="5"/>
+      <c r="B573" s="4"/>
     </row>
     <row r="574" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B574" s="5"/>
+      <c r="B574" s="4"/>
     </row>
     <row r="575" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B575" s="5"/>
+      <c r="B575" s="4"/>
     </row>
     <row r="576" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B576" s="5"/>
+      <c r="B576" s="4"/>
     </row>
     <row r="577" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B577" s="5"/>
+      <c r="B577" s="4"/>
     </row>
     <row r="578" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B578" s="5"/>
+      <c r="B578" s="4"/>
     </row>
     <row r="579" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B579" s="5"/>
+      <c r="B579" s="4"/>
     </row>
     <row r="580" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B580" s="5"/>
+      <c r="B580" s="4"/>
     </row>
     <row r="581" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B581" s="5"/>
+      <c r="B581" s="4"/>
     </row>
     <row r="582" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B582" s="5"/>
+      <c r="B582" s="4"/>
     </row>
     <row r="583" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B583" s="5"/>
+      <c r="B583" s="4"/>
     </row>
     <row r="584" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B584" s="5"/>
+      <c r="B584" s="4"/>
     </row>
     <row r="585" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B585" s="5"/>
+      <c r="B585" s="4"/>
     </row>
     <row r="586" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B586" s="5"/>
+      <c r="B586" s="4"/>
     </row>
     <row r="587" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B587" s="5"/>
+      <c r="B587" s="4"/>
     </row>
     <row r="588" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B588" s="5"/>
+      <c r="B588" s="4"/>
     </row>
     <row r="589" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B589" s="5"/>
+      <c r="B589" s="4"/>
     </row>
     <row r="590" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B590" s="5"/>
+      <c r="B590" s="4"/>
     </row>
     <row r="591" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B591" s="5"/>
+      <c r="B591" s="4"/>
     </row>
     <row r="592" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B592" s="5"/>
+      <c r="B592" s="4"/>
     </row>
     <row r="593" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B593" s="5"/>
+      <c r="B593" s="4"/>
     </row>
     <row r="594" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B594" s="5"/>
+      <c r="B594" s="4"/>
     </row>
     <row r="595" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B595" s="5"/>
+      <c r="B595" s="4"/>
     </row>
     <row r="596" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B596" s="5"/>
+      <c r="B596" s="4"/>
     </row>
     <row r="597" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B597" s="5"/>
+      <c r="B597" s="4"/>
     </row>
     <row r="598" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B598" s="5"/>
+      <c r="B598" s="4"/>
     </row>
     <row r="599" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B599" s="5"/>
+      <c r="B599" s="4"/>
     </row>
     <row r="600" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B600" s="5"/>
+      <c r="B600" s="4"/>
     </row>
     <row r="601" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B601" s="5"/>
+      <c r="B601" s="4"/>
     </row>
     <row r="602" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B602" s="5"/>
+      <c r="B602" s="4"/>
     </row>
     <row r="603" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B603" s="5"/>
+      <c r="B603" s="4"/>
     </row>
     <row r="604" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B604" s="5"/>
+      <c r="B604" s="4"/>
     </row>
     <row r="605" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B605" s="5"/>
+      <c r="B605" s="4"/>
     </row>
     <row r="606" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B606" s="5"/>
+      <c r="B606" s="4"/>
     </row>
     <row r="607" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B607" s="5"/>
+      <c r="B607" s="4"/>
     </row>
     <row r="608" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B608" s="5"/>
+      <c r="B608" s="4"/>
     </row>
     <row r="609" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B609" s="5"/>
+      <c r="B609" s="4"/>
     </row>
     <row r="610" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B610" s="5"/>
+      <c r="B610" s="4"/>
     </row>
     <row r="611" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B611" s="5"/>
+      <c r="B611" s="4"/>
     </row>
     <row r="612" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B612" s="5"/>
+      <c r="B612" s="4"/>
     </row>
     <row r="613" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B613" s="5"/>
+      <c r="B613" s="4"/>
     </row>
     <row r="614" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B614" s="5"/>
+      <c r="B614" s="4"/>
     </row>
     <row r="615" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B615" s="5"/>
+      <c r="B615" s="4"/>
     </row>
     <row r="616" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B616" s="5"/>
+      <c r="B616" s="4"/>
     </row>
     <row r="617" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B617" s="5"/>
+      <c r="B617" s="4"/>
     </row>
     <row r="618" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B618" s="5"/>
+      <c r="B618" s="4"/>
     </row>
     <row r="619" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B619" s="5"/>
+      <c r="B619" s="4"/>
     </row>
     <row r="620" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B620" s="5"/>
+      <c r="B620" s="4"/>
     </row>
     <row r="621" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B621" s="5"/>
+      <c r="B621" s="4"/>
     </row>
     <row r="622" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B622" s="5"/>
+      <c r="B622" s="4"/>
     </row>
     <row r="623" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B623" s="5"/>
+      <c r="B623" s="4"/>
     </row>
     <row r="624" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B624" s="5"/>
+      <c r="B624" s="4"/>
     </row>
     <row r="625" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B625" s="5"/>
+      <c r="B625" s="4"/>
     </row>
     <row r="626" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B626" s="5"/>
+      <c r="B626" s="4"/>
     </row>
     <row r="627" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B627" s="5"/>
+      <c r="B627" s="4"/>
     </row>
     <row r="628" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B628" s="5"/>
+      <c r="B628" s="4"/>
     </row>
     <row r="629" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B629" s="5"/>
+      <c r="B629" s="4"/>
     </row>
     <row r="630" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B630" s="5"/>
+      <c r="B630" s="4"/>
     </row>
     <row r="631" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B631" s="5"/>
+      <c r="B631" s="4"/>
     </row>
     <row r="632" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B632" s="5"/>
+      <c r="B632" s="4"/>
     </row>
     <row r="633" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B633" s="5"/>
+      <c r="B633" s="4"/>
     </row>
     <row r="634" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B634" s="5"/>
+      <c r="B634" s="4"/>
     </row>
     <row r="635" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B635" s="5"/>
+      <c r="B635" s="4"/>
     </row>
     <row r="636" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B636" s="5"/>
+      <c r="B636" s="4"/>
     </row>
     <row r="637" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B637" s="5"/>
+      <c r="B637" s="4"/>
     </row>
     <row r="638" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B638" s="5"/>
+      <c r="B638" s="4"/>
     </row>
     <row r="639" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B639" s="5"/>
+      <c r="B639" s="4"/>
     </row>
     <row r="640" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B640" s="5"/>
+      <c r="B640" s="4"/>
     </row>
     <row r="641" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B641" s="5"/>
+      <c r="B641" s="4"/>
     </row>
     <row r="642" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B642" s="5"/>
+      <c r="B642" s="4"/>
     </row>
     <row r="643" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B643" s="5"/>
+      <c r="B643" s="4"/>
     </row>
     <row r="644" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B644" s="5"/>
+      <c r="B644" s="4"/>
     </row>
     <row r="645" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B645" s="5"/>
+      <c r="B645" s="4"/>
     </row>
     <row r="646" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B646" s="5"/>
+      <c r="B646" s="4"/>
     </row>
     <row r="647" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B647" s="5"/>
+      <c r="B647" s="4"/>
     </row>
     <row r="648" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B648" s="5"/>
+      <c r="B648" s="4"/>
     </row>
     <row r="649" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B649" s="5"/>
+      <c r="B649" s="4"/>
     </row>
     <row r="650" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B650" s="5"/>
+      <c r="B650" s="4"/>
     </row>
     <row r="651" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B651" s="5"/>
+      <c r="B651" s="4"/>
     </row>
     <row r="652" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B652" s="5"/>
+      <c r="B652" s="4"/>
     </row>
     <row r="653" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B653" s="5"/>
+      <c r="B653" s="4"/>
     </row>
     <row r="654" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B654" s="5"/>
+      <c r="B654" s="4"/>
     </row>
     <row r="655" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B655" s="5"/>
+      <c r="B655" s="4"/>
     </row>
     <row r="656" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B656" s="5"/>
+      <c r="B656" s="4"/>
     </row>
     <row r="657" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B657" s="5"/>
+      <c r="B657" s="4"/>
     </row>
     <row r="658" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B658" s="5"/>
+      <c r="B658" s="4"/>
     </row>
     <row r="659" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B659" s="5"/>
+      <c r="B659" s="4"/>
     </row>
     <row r="660" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B660" s="5"/>
+      <c r="B660" s="4"/>
     </row>
     <row r="661" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B661" s="5"/>
+      <c r="B661" s="4"/>
     </row>
     <row r="662" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B662" s="5"/>
+      <c r="B662" s="4"/>
     </row>
     <row r="663" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B663" s="5"/>
+      <c r="B663" s="4"/>
     </row>
     <row r="664" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B664" s="5"/>
+      <c r="B664" s="4"/>
     </row>
     <row r="665" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B665" s="5"/>
+      <c r="B665" s="4"/>
     </row>
     <row r="666" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B666" s="5"/>
+      <c r="B666" s="4"/>
     </row>
     <row r="667" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B667" s="5"/>
+      <c r="B667" s="4"/>
     </row>
     <row r="668" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B668" s="5"/>
+      <c r="B668" s="4"/>
     </row>
     <row r="669" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B669" s="5"/>
+      <c r="B669" s="4"/>
     </row>
     <row r="670" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B670" s="5"/>
+      <c r="B670" s="4"/>
     </row>
     <row r="671" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B671" s="5"/>
+      <c r="B671" s="4"/>
     </row>
     <row r="672" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B672" s="5"/>
+      <c r="B672" s="4"/>
     </row>
     <row r="673" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B673" s="5"/>
+      <c r="B673" s="4"/>
     </row>
     <row r="674" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B674" s="5"/>
+      <c r="B674" s="4"/>
     </row>
     <row r="675" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B675" s="5"/>
+      <c r="B675" s="4"/>
     </row>
     <row r="676" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B676" s="5"/>
+      <c r="B676" s="4"/>
     </row>
     <row r="677" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B677" s="5"/>
+      <c r="B677" s="4"/>
     </row>
     <row r="678" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B678" s="5"/>
+      <c r="B678" s="4"/>
     </row>
     <row r="679" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B679" s="5"/>
+      <c r="B679" s="4"/>
     </row>
     <row r="680" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B680" s="5"/>
+      <c r="B680" s="4"/>
     </row>
     <row r="681" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B681" s="5"/>
+      <c r="B681" s="4"/>
     </row>
     <row r="682" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B682" s="5"/>
+      <c r="B682" s="4"/>
     </row>
     <row r="683" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B683" s="5"/>
+      <c r="B683" s="4"/>
     </row>
     <row r="684" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B684" s="5"/>
+      <c r="B684" s="4"/>
     </row>
     <row r="685" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B685" s="5"/>
+      <c r="B685" s="4"/>
     </row>
     <row r="686" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B686" s="5"/>
+      <c r="B686" s="4"/>
     </row>
     <row r="687" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B687" s="5"/>
+      <c r="B687" s="4"/>
     </row>
     <row r="688" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B688" s="5"/>
+      <c r="B688" s="4"/>
     </row>
     <row r="689" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B689" s="5"/>
+      <c r="B689" s="4"/>
     </row>
     <row r="690" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B690" s="5"/>
+      <c r="B690" s="4"/>
     </row>
     <row r="691" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B691" s="5"/>
+      <c r="B691" s="4"/>
     </row>
     <row r="692" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B692" s="5"/>
+      <c r="B692" s="4"/>
     </row>
     <row r="693" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B693" s="5"/>
+      <c r="B693" s="4"/>
     </row>
     <row r="694" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B694" s="5"/>
+      <c r="B694" s="4"/>
     </row>
     <row r="695" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B695" s="5"/>
+      <c r="B695" s="4"/>
     </row>
     <row r="696" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B696" s="5"/>
+      <c r="B696" s="4"/>
     </row>
     <row r="697" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B697" s="5"/>
+      <c r="B697" s="4"/>
     </row>
     <row r="698" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B698" s="5"/>
+      <c r="B698" s="4"/>
     </row>
     <row r="699" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B699" s="5"/>
+      <c r="B699" s="4"/>
     </row>
     <row r="700" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B700" s="5"/>
+      <c r="B700" s="4"/>
     </row>
     <row r="701" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B701" s="5"/>
+      <c r="B701" s="4"/>
     </row>
     <row r="702" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B702" s="5"/>
+      <c r="B702" s="4"/>
     </row>
     <row r="703" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B703" s="5"/>
+      <c r="B703" s="4"/>
     </row>
     <row r="704" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B704" s="5"/>
+      <c r="B704" s="4"/>
     </row>
     <row r="705" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B705" s="5"/>
+      <c r="B705" s="4"/>
     </row>
     <row r="706" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B706" s="5"/>
+      <c r="B706" s="4"/>
     </row>
     <row r="707" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B707" s="5"/>
+      <c r="B707" s="4"/>
     </row>
     <row r="708" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B708" s="5"/>
+      <c r="B708" s="4"/>
     </row>
     <row r="709" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B709" s="5"/>
+      <c r="B709" s="4"/>
     </row>
     <row r="710" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B710" s="5"/>
+      <c r="B710" s="4"/>
     </row>
     <row r="711" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B711" s="5"/>
+      <c r="B711" s="4"/>
     </row>
     <row r="712" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B712" s="5"/>
+      <c r="B712" s="4"/>
     </row>
     <row r="713" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B713" s="5"/>
+      <c r="B713" s="4"/>
     </row>
     <row r="714" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B714" s="5"/>
+      <c r="B714" s="4"/>
     </row>
     <row r="715" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B715" s="5"/>
+      <c r="B715" s="4"/>
     </row>
     <row r="716" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B716" s="5"/>
+      <c r="B716" s="4"/>
     </row>
     <row r="717" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B717" s="5"/>
+      <c r="B717" s="4"/>
     </row>
     <row r="718" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B718" s="5"/>
+      <c r="B718" s="4"/>
     </row>
     <row r="719" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B719" s="5"/>
+      <c r="B719" s="4"/>
     </row>
     <row r="720" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B720" s="5"/>
+      <c r="B720" s="4"/>
     </row>
     <row r="721" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B721" s="5"/>
+      <c r="B721" s="4"/>
     </row>
     <row r="722" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B722" s="5"/>
+      <c r="B722" s="4"/>
     </row>
     <row r="723" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B723" s="5"/>
+      <c r="B723" s="4"/>
     </row>
     <row r="724" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B724" s="5"/>
+      <c r="B724" s="4"/>
     </row>
     <row r="725" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B725" s="5"/>
+      <c r="B725" s="4"/>
     </row>
     <row r="726" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B726" s="5"/>
+      <c r="B726" s="4"/>
     </row>
     <row r="727" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B727" s="5"/>
+      <c r="B727" s="4"/>
     </row>
     <row r="728" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B728" s="5"/>
+      <c r="B728" s="4"/>
     </row>
     <row r="729" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B729" s="5"/>
+      <c r="B729" s="4"/>
     </row>
     <row r="730" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B730" s="5"/>
+      <c r="B730" s="4"/>
     </row>
     <row r="731" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B731" s="5"/>
+      <c r="B731" s="4"/>
     </row>
     <row r="732" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B732" s="5"/>
+      <c r="B732" s="4"/>
     </row>
     <row r="733" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B733" s="5"/>
+      <c r="B733" s="4"/>
     </row>
     <row r="734" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B734" s="5"/>
+      <c r="B734" s="4"/>
     </row>
     <row r="735" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B735" s="5"/>
+      <c r="B735" s="4"/>
     </row>
     <row r="736" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B736" s="5"/>
+      <c r="B736" s="4"/>
     </row>
     <row r="737" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B737" s="5"/>
+      <c r="B737" s="4"/>
     </row>
     <row r="738" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B738" s="5"/>
+      <c r="B738" s="4"/>
     </row>
     <row r="739" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B739" s="5"/>
+      <c r="B739" s="4"/>
     </row>
     <row r="740" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B740" s="5"/>
+      <c r="B740" s="4"/>
     </row>
     <row r="741" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B741" s="5"/>
+      <c r="B741" s="4"/>
     </row>
     <row r="742" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B742" s="5"/>
+      <c r="B742" s="4"/>
     </row>
     <row r="743" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B743" s="5"/>
+      <c r="B743" s="4"/>
     </row>
     <row r="744" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B744" s="5"/>
+      <c r="B744" s="4"/>
     </row>
     <row r="745" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B745" s="5"/>
+      <c r="B745" s="4"/>
     </row>
     <row r="746" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B746" s="5"/>
+      <c r="B746" s="4"/>
     </row>
     <row r="747" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B747" s="5"/>
+      <c r="B747" s="4"/>
     </row>
     <row r="748" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B748" s="5"/>
+      <c r="B748" s="4"/>
     </row>
     <row r="749" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B749" s="5"/>
+      <c r="B749" s="4"/>
     </row>
     <row r="750" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B750" s="5"/>
+      <c r="B750" s="4"/>
     </row>
     <row r="751" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B751" s="5"/>
+      <c r="B751" s="4"/>
     </row>
     <row r="752" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B752" s="5"/>
+      <c r="B752" s="4"/>
     </row>
     <row r="753" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B753" s="5"/>
+      <c r="B753" s="4"/>
     </row>
     <row r="754" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B754" s="5"/>
+      <c r="B754" s="4"/>
     </row>
     <row r="755" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B755" s="5"/>
+      <c r="B755" s="4"/>
     </row>
     <row r="756" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B756" s="5"/>
+      <c r="B756" s="4"/>
     </row>
     <row r="757" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B757" s="5"/>
+      <c r="B757" s="4"/>
     </row>
     <row r="758" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B758" s="5"/>
+      <c r="B758" s="4"/>
     </row>
     <row r="759" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B759" s="5"/>
+      <c r="B759" s="4"/>
     </row>
     <row r="760" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B760" s="5"/>
+      <c r="B760" s="4"/>
     </row>
     <row r="761" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B761" s="5"/>
+      <c r="B761" s="4"/>
     </row>
     <row r="762" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B762" s="5"/>
+      <c r="B762" s="4"/>
     </row>
     <row r="763" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B763" s="5"/>
+      <c r="B763" s="4"/>
     </row>
     <row r="764" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B764" s="5"/>
+      <c r="B764" s="4"/>
     </row>
     <row r="765" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B765" s="5"/>
+      <c r="B765" s="4"/>
     </row>
     <row r="766" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B766" s="5"/>
+      <c r="B766" s="4"/>
     </row>
     <row r="767" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B767" s="5"/>
+      <c r="B767" s="4"/>
     </row>
     <row r="768" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B768" s="5"/>
+      <c r="B768" s="4"/>
     </row>
     <row r="769" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B769" s="5"/>
+      <c r="B769" s="4"/>
     </row>
     <row r="770" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B770" s="5"/>
+      <c r="B770" s="4"/>
     </row>
     <row r="771" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B771" s="5"/>
+      <c r="B771" s="4"/>
     </row>
     <row r="772" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B772" s="5"/>
+      <c r="B772" s="4"/>
     </row>
     <row r="773" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B773" s="5"/>
+      <c r="B773" s="4"/>
     </row>
     <row r="774" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B774" s="5"/>
+      <c r="B774" s="4"/>
     </row>
     <row r="775" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B775" s="5"/>
+      <c r="B775" s="4"/>
     </row>
     <row r="776" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B776" s="5"/>
+      <c r="B776" s="4"/>
     </row>
     <row r="777" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B777" s="5"/>
+      <c r="B777" s="4"/>
     </row>
     <row r="778" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B778" s="5"/>
+      <c r="B778" s="4"/>
     </row>
     <row r="779" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B779" s="5"/>
+      <c r="B779" s="4"/>
     </row>
     <row r="780" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B780" s="5"/>
+      <c r="B780" s="4"/>
     </row>
     <row r="781" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B781" s="5"/>
+      <c r="B781" s="4"/>
     </row>
     <row r="782" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B782" s="5"/>
+      <c r="B782" s="4"/>
     </row>
     <row r="783" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B783" s="5"/>
+      <c r="B783" s="4"/>
     </row>
     <row r="784" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B784" s="5"/>
+      <c r="B784" s="4"/>
     </row>
     <row r="785" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B785" s="5"/>
+      <c r="B785" s="4"/>
     </row>
     <row r="786" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B786" s="5"/>
+      <c r="B786" s="4"/>
     </row>
     <row r="787" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B787" s="5"/>
+      <c r="B787" s="4"/>
     </row>
     <row r="788" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B788" s="5"/>
+      <c r="B788" s="4"/>
     </row>
     <row r="789" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B789" s="5"/>
+      <c r="B789" s="4"/>
     </row>
     <row r="790" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B790" s="5"/>
+      <c r="B790" s="4"/>
     </row>
     <row r="791" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B791" s="5"/>
+      <c r="B791" s="4"/>
     </row>
     <row r="792" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B792" s="5"/>
+      <c r="B792" s="4"/>
     </row>
     <row r="793" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B793" s="5"/>
+      <c r="B793" s="4"/>
     </row>
     <row r="794" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B794" s="5"/>
+      <c r="B794" s="4"/>
     </row>
     <row r="795" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B795" s="5"/>
+      <c r="B795" s="4"/>
     </row>
     <row r="796" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B796" s="5"/>
+      <c r="B796" s="4"/>
     </row>
     <row r="797" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B797" s="5"/>
+      <c r="B797" s="4"/>
     </row>
     <row r="798" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B798" s="5"/>
+      <c r="B798" s="4"/>
     </row>
     <row r="799" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B799" s="5"/>
+      <c r="B799" s="4"/>
     </row>
     <row r="800" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B800" s="5"/>
+      <c r="B800" s="4"/>
     </row>
     <row r="801" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B801" s="5"/>
+      <c r="B801" s="4"/>
     </row>
     <row r="802" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B802" s="5"/>
+      <c r="B802" s="4"/>
     </row>
     <row r="803" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B803" s="5"/>
+      <c r="B803" s="4"/>
     </row>
     <row r="804" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B804" s="5"/>
+      <c r="B804" s="4"/>
     </row>
     <row r="805" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B805" s="5"/>
+      <c r="B805" s="4"/>
     </row>
     <row r="806" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B806" s="5"/>
+      <c r="B806" s="4"/>
     </row>
     <row r="807" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B807" s="5"/>
+      <c r="B807" s="4"/>
     </row>
     <row r="808" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B808" s="5"/>
+      <c r="B808" s="4"/>
     </row>
     <row r="809" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B809" s="5"/>
+      <c r="B809" s="4"/>
     </row>
     <row r="810" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B810" s="5"/>
+      <c r="B810" s="4"/>
     </row>
     <row r="811" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B811" s="5"/>
+      <c r="B811" s="4"/>
     </row>
     <row r="812" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B812" s="5"/>
+      <c r="B812" s="4"/>
     </row>
     <row r="813" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B813" s="5"/>
+      <c r="B813" s="4"/>
     </row>
     <row r="814" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B814" s="5"/>
+      <c r="B814" s="4"/>
     </row>
     <row r="815" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B815" s="5"/>
+      <c r="B815" s="4"/>
     </row>
     <row r="816" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B816" s="5"/>
+      <c r="B816" s="4"/>
     </row>
     <row r="817" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B817" s="5"/>
+      <c r="B817" s="4"/>
     </row>
     <row r="818" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B818" s="5"/>
+      <c r="B818" s="4"/>
     </row>
     <row r="819" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B819" s="5"/>
+      <c r="B819" s="4"/>
     </row>
     <row r="820" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B820" s="5"/>
+      <c r="B820" s="4"/>
     </row>
     <row r="821" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B821" s="5"/>
+      <c r="B821" s="4"/>
     </row>
     <row r="822" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B822" s="5"/>
+      <c r="B822" s="4"/>
     </row>
     <row r="823" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B823" s="5"/>
+      <c r="B823" s="4"/>
     </row>
     <row r="824" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B824" s="5"/>
+      <c r="B824" s="4"/>
     </row>
     <row r="825" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B825" s="5"/>
+      <c r="B825" s="4"/>
     </row>
     <row r="826" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B826" s="5"/>
+      <c r="B826" s="4"/>
     </row>
     <row r="827" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B827" s="5"/>
+      <c r="B827" s="4"/>
     </row>
     <row r="828" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B828" s="5"/>
+      <c r="B828" s="4"/>
     </row>
     <row r="829" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B829" s="5"/>
+      <c r="B829" s="4"/>
     </row>
     <row r="830" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B830" s="5"/>
+      <c r="B830" s="4"/>
     </row>
     <row r="831" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B831" s="5"/>
+      <c r="B831" s="4"/>
     </row>
     <row r="832" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B832" s="5"/>
+      <c r="B832" s="4"/>
     </row>
     <row r="833" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B833" s="5"/>
+      <c r="B833" s="4"/>
     </row>
     <row r="834" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B834" s="5"/>
+      <c r="B834" s="4"/>
     </row>
     <row r="835" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B835" s="5"/>
+      <c r="B835" s="4"/>
     </row>
     <row r="836" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B836" s="5"/>
+      <c r="B836" s="4"/>
     </row>
     <row r="837" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B837" s="5"/>
+      <c r="B837" s="4"/>
     </row>
     <row r="838" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B838" s="5"/>
+      <c r="B838" s="4"/>
     </row>
     <row r="839" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B839" s="5"/>
+      <c r="B839" s="4"/>
     </row>
     <row r="840" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B840" s="5"/>
+      <c r="B840" s="4"/>
     </row>
     <row r="841" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B841" s="5"/>
+      <c r="B841" s="4"/>
     </row>
     <row r="842" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B842" s="5"/>
+      <c r="B842" s="4"/>
     </row>
     <row r="843" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B843" s="5"/>
+      <c r="B843" s="4"/>
     </row>
     <row r="844" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B844" s="5"/>
+      <c r="B844" s="4"/>
     </row>
     <row r="845" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B845" s="5"/>
+      <c r="B845" s="4"/>
     </row>
     <row r="846" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B846" s="5"/>
+      <c r="B846" s="4"/>
     </row>
     <row r="847" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B847" s="5"/>
+      <c r="B847" s="4"/>
     </row>
     <row r="848" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B848" s="5"/>
+      <c r="B848" s="4"/>
     </row>
     <row r="849" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B849" s="5"/>
+      <c r="B849" s="4"/>
     </row>
     <row r="850" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B850" s="5"/>
+      <c r="B850" s="4"/>
     </row>
     <row r="851" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B851" s="5"/>
+      <c r="B851" s="4"/>
     </row>
     <row r="852" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B852" s="5"/>
+      <c r="B852" s="4"/>
     </row>
     <row r="853" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B853" s="5"/>
+      <c r="B853" s="4"/>
     </row>
     <row r="854" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B854" s="5"/>
+      <c r="B854" s="4"/>
     </row>
     <row r="855" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B855" s="5"/>
+      <c r="B855" s="4"/>
     </row>
     <row r="856" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B856" s="5"/>
+      <c r="B856" s="4"/>
     </row>
     <row r="857" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B857" s="5"/>
+      <c r="B857" s="4"/>
     </row>
     <row r="858" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B858" s="5"/>
+      <c r="B858" s="4"/>
     </row>
     <row r="859" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B859" s="5"/>
+      <c r="B859" s="4"/>
     </row>
     <row r="860" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B860" s="5"/>
+      <c r="B860" s="4"/>
     </row>
     <row r="861" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B861" s="5"/>
+      <c r="B861" s="4"/>
     </row>
     <row r="862" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B862" s="5"/>
+      <c r="B862" s="4"/>
     </row>
     <row r="863" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B863" s="5"/>
+      <c r="B863" s="4"/>
     </row>
     <row r="864" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B864" s="5"/>
+      <c r="B864" s="4"/>
     </row>
     <row r="865" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B865" s="5"/>
+      <c r="B865" s="4"/>
     </row>
     <row r="866" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B866" s="5"/>
+      <c r="B866" s="4"/>
     </row>
     <row r="867" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B867" s="5"/>
+      <c r="B867" s="4"/>
     </row>
     <row r="868" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B868" s="5"/>
+      <c r="B868" s="4"/>
     </row>
     <row r="869" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B869" s="5"/>
+      <c r="B869" s="4"/>
     </row>
     <row r="870" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B870" s="5"/>
+      <c r="B870" s="4"/>
     </row>
     <row r="871" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B871" s="5"/>
+      <c r="B871" s="4"/>
     </row>
     <row r="872" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B872" s="5"/>
+      <c r="B872" s="4"/>
     </row>
     <row r="873" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B873" s="5"/>
+      <c r="B873" s="4"/>
     </row>
     <row r="874" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B874" s="5"/>
+      <c r="B874" s="4"/>
     </row>
     <row r="875" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B875" s="5"/>
+      <c r="B875" s="4"/>
     </row>
     <row r="876" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B876" s="5"/>
+      <c r="B876" s="4"/>
     </row>
     <row r="877" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B877" s="5"/>
+      <c r="B877" s="4"/>
     </row>
     <row r="878" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B878" s="5"/>
+      <c r="B878" s="4"/>
     </row>
     <row r="879" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B879" s="5"/>
+      <c r="B879" s="4"/>
     </row>
     <row r="880" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B880" s="5"/>
+      <c r="B880" s="4"/>
     </row>
     <row r="881" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B881" s="5"/>
+      <c r="B881" s="4"/>
     </row>
     <row r="882" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B882" s="5"/>
+      <c r="B882" s="4"/>
     </row>
     <row r="883" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B883" s="5"/>
+      <c r="B883" s="4"/>
     </row>
     <row r="884" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B884" s="5"/>
+      <c r="B884" s="4"/>
     </row>
     <row r="885" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B885" s="5"/>
+      <c r="B885" s="4"/>
     </row>
     <row r="886" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B886" s="5"/>
+      <c r="B886" s="4"/>
     </row>
     <row r="887" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B887" s="5"/>
+      <c r="B887" s="4"/>
     </row>
     <row r="888" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B888" s="5"/>
+      <c r="B888" s="4"/>
     </row>
     <row r="889" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B889" s="5"/>
+      <c r="B889" s="4"/>
     </row>
     <row r="890" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B890" s="5"/>
+      <c r="B890" s="4"/>
     </row>
     <row r="891" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B891" s="5"/>
+      <c r="B891" s="4"/>
     </row>
     <row r="892" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B892" s="5"/>
+      <c r="B892" s="4"/>
     </row>
     <row r="893" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B893" s="5"/>
+      <c r="B893" s="4"/>
     </row>
     <row r="894" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B894" s="5"/>
+      <c r="B894" s="4"/>
     </row>
     <row r="895" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B895" s="5"/>
+      <c r="B895" s="4"/>
     </row>
     <row r="896" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B896" s="5"/>
+      <c r="B896" s="4"/>
     </row>
     <row r="897" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B897" s="5"/>
+      <c r="B897" s="4"/>
     </row>
     <row r="898" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B898" s="5"/>
+      <c r="B898" s="4"/>
     </row>
     <row r="899" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B899" s="5"/>
+      <c r="B899" s="4"/>
     </row>
     <row r="900" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B900" s="5"/>
+      <c r="B900" s="4"/>
     </row>
     <row r="901" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B901" s="5"/>
+      <c r="B901" s="4"/>
     </row>
     <row r="902" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B902" s="5"/>
+      <c r="B902" s="4"/>
     </row>
     <row r="903" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B903" s="5"/>
+      <c r="B903" s="4"/>
     </row>
     <row r="904" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B904" s="5"/>
+      <c r="B904" s="4"/>
     </row>
     <row r="905" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B905" s="5"/>
+      <c r="B905" s="4"/>
     </row>
     <row r="906" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B906" s="5"/>
+      <c r="B906" s="4"/>
     </row>
     <row r="907" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B907" s="5"/>
+      <c r="B907" s="4"/>
     </row>
     <row r="908" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B908" s="5"/>
+      <c r="B908" s="4"/>
     </row>
     <row r="909" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B909" s="5"/>
+      <c r="B909" s="4"/>
     </row>
     <row r="910" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B910" s="5"/>
+      <c r="B910" s="4"/>
     </row>
     <row r="911" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B911" s="5"/>
+      <c r="B911" s="4"/>
     </row>
     <row r="912" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B912" s="5"/>
+      <c r="B912" s="4"/>
     </row>
     <row r="913" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B913" s="5"/>
+      <c r="B913" s="4"/>
     </row>
     <row r="914" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B914" s="5"/>
+      <c r="B914" s="4"/>
     </row>
     <row r="915" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B915" s="5"/>
+      <c r="B915" s="4"/>
     </row>
     <row r="916" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B916" s="5"/>
+      <c r="B916" s="4"/>
     </row>
     <row r="917" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B917" s="5"/>
+      <c r="B917" s="4"/>
     </row>
     <row r="918" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B918" s="5"/>
+      <c r="B918" s="4"/>
     </row>
     <row r="919" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B919" s="5"/>
+      <c r="B919" s="4"/>
     </row>
     <row r="920" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B920" s="5"/>
+      <c r="B920" s="4"/>
     </row>
     <row r="921" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B921" s="5"/>
+      <c r="B921" s="4"/>
     </row>
     <row r="922" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B922" s="5"/>
+      <c r="B922" s="4"/>
     </row>
     <row r="923" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B923" s="5"/>
+      <c r="B923" s="4"/>
     </row>
     <row r="924" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B924" s="5"/>
+      <c r="B924" s="4"/>
     </row>
     <row r="925" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B925" s="5"/>
+      <c r="B925" s="4"/>
     </row>
     <row r="926" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B926" s="5"/>
+      <c r="B926" s="4"/>
     </row>
     <row r="927" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B927" s="5"/>
+      <c r="B927" s="4"/>
     </row>
     <row r="928" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B928" s="5"/>
+      <c r="B928" s="4"/>
     </row>
     <row r="929" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B929" s="5"/>
+      <c r="B929" s="4"/>
     </row>
     <row r="930" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B930" s="5"/>
+      <c r="B930" s="4"/>
     </row>
     <row r="931" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B931" s="5"/>
+      <c r="B931" s="4"/>
     </row>
     <row r="932" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B932" s="5"/>
+      <c r="B932" s="4"/>
     </row>
     <row r="933" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B933" s="5"/>
+      <c r="B933" s="4"/>
     </row>
     <row r="934" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B934" s="5"/>
+      <c r="B934" s="4"/>
     </row>
     <row r="935" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B935" s="5"/>
+      <c r="B935" s="4"/>
     </row>
     <row r="936" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B936" s="5"/>
+      <c r="B936" s="4"/>
     </row>
     <row r="937" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B937" s="5"/>
+      <c r="B937" s="4"/>
     </row>
     <row r="938" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B938" s="5"/>
+      <c r="B938" s="4"/>
     </row>
     <row r="939" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B939" s="5"/>
+      <c r="B939" s="4"/>
     </row>
     <row r="940" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B940" s="5"/>
+      <c r="B940" s="4"/>
     </row>
     <row r="941" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B941" s="5"/>
+      <c r="B941" s="4"/>
     </row>
     <row r="942" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B942" s="5"/>
+      <c r="B942" s="4"/>
     </row>
     <row r="943" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B943" s="5"/>
+      <c r="B943" s="4"/>
     </row>
     <row r="944" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B944" s="5"/>
+      <c r="B944" s="4"/>
     </row>
     <row r="945" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B945" s="5"/>
+      <c r="B945" s="4"/>
     </row>
     <row r="946" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B946" s="5"/>
+      <c r="B946" s="4"/>
     </row>
     <row r="947" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B947" s="5"/>
+      <c r="B947" s="4"/>
     </row>
     <row r="948" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B948" s="5"/>
+      <c r="B948" s="4"/>
     </row>
     <row r="949" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B949" s="5"/>
+      <c r="B949" s="4"/>
     </row>
     <row r="950" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B950" s="5"/>
+      <c r="B950" s="4"/>
     </row>
     <row r="951" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B951" s="5"/>
+      <c r="B951" s="4"/>
     </row>
     <row r="952" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B952" s="5"/>
+      <c r="B952" s="4"/>
     </row>
     <row r="953" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B953" s="5"/>
+      <c r="B953" s="4"/>
     </row>
     <row r="954" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B954" s="5"/>
+      <c r="B954" s="4"/>
     </row>
     <row r="955" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B955" s="5"/>
+      <c r="B955" s="4"/>
     </row>
     <row r="956" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B956" s="5"/>
+      <c r="B956" s="4"/>
     </row>
     <row r="957" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B957" s="5"/>
+      <c r="B957" s="4"/>
     </row>
     <row r="958" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B958" s="5"/>
+      <c r="B958" s="4"/>
     </row>
     <row r="959" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B959" s="5"/>
+      <c r="B959" s="4"/>
     </row>
     <row r="960" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B960" s="5"/>
+      <c r="B960" s="4"/>
     </row>
     <row r="961" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B961" s="5"/>
+      <c r="B961" s="4"/>
     </row>
     <row r="962" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B962" s="5"/>
+      <c r="B962" s="4"/>
     </row>
     <row r="963" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B963" s="5"/>
+      <c r="B963" s="4"/>
     </row>
     <row r="964" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B964" s="5"/>
+      <c r="B964" s="4"/>
     </row>
     <row r="965" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B965" s="5"/>
+      <c r="B965" s="4"/>
     </row>
     <row r="966" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B966" s="5"/>
+      <c r="B966" s="4"/>
     </row>
     <row r="967" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B967" s="5"/>
+      <c r="B967" s="4"/>
     </row>
     <row r="968" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B968" s="5"/>
+      <c r="B968" s="4"/>
     </row>
     <row r="969" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B969" s="5"/>
+      <c r="B969" s="4"/>
     </row>
     <row r="970" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B970" s="5"/>
+      <c r="B970" s="4"/>
     </row>
     <row r="971" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B971" s="5"/>
+      <c r="B971" s="4"/>
     </row>
     <row r="972" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B972" s="5"/>
+      <c r="B972" s="4"/>
     </row>
     <row r="973" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B973" s="5"/>
+      <c r="B973" s="4"/>
     </row>
     <row r="974" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B974" s="5"/>
+      <c r="B974" s="4"/>
     </row>
     <row r="975" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B975" s="5"/>
+      <c r="B975" s="4"/>
     </row>
     <row r="976" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B976" s="5"/>
+      <c r="B976" s="4"/>
     </row>
     <row r="977" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B977" s="5"/>
+      <c r="B977" s="4"/>
     </row>
     <row r="978" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B978" s="5"/>
+      <c r="B978" s="4"/>
     </row>
     <row r="979" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B979" s="5"/>
+      <c r="B979" s="4"/>
     </row>
     <row r="980" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B980" s="5"/>
+      <c r="B980" s="4"/>
     </row>
     <row r="981" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B981" s="5"/>
+      <c r="B981" s="4"/>
     </row>
     <row r="982" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B982" s="5"/>
+      <c r="B982" s="4"/>
     </row>
     <row r="983" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B983" s="5"/>
+      <c r="B983" s="4"/>
     </row>
     <row r="984" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B984" s="5"/>
+      <c r="B984" s="4"/>
     </row>
     <row r="985" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B985" s="5"/>
+      <c r="B985" s="4"/>
     </row>
     <row r="986" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B986" s="5"/>
+      <c r="B986" s="4"/>
     </row>
     <row r="987" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B987" s="5"/>
+      <c r="B987" s="4"/>
     </row>
     <row r="988" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B988" s="5"/>
+      <c r="B988" s="4"/>
     </row>
     <row r="989" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B989" s="5"/>
+      <c r="B989" s="4"/>
     </row>
     <row r="990" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B990" s="5"/>
+      <c r="B990" s="4"/>
     </row>
     <row r="991" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B991" s="5"/>
+      <c r="B991" s="4"/>
     </row>
     <row r="992" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B992" s="5"/>
+      <c r="B992" s="4"/>
     </row>
     <row r="993" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B993" s="5"/>
+      <c r="B993" s="4"/>
     </row>
     <row r="994" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B994" s="5"/>
+      <c r="B994" s="4"/>
     </row>
     <row r="995" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B995" s="5"/>
+      <c r="B995" s="4"/>
     </row>
     <row r="996" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B996" s="5"/>
+      <c r="B996" s="4"/>
     </row>
     <row r="997" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B997" s="5"/>
+      <c r="B997" s="4"/>
     </row>
     <row r="998" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B998" s="5"/>
+      <c r="B998" s="4"/>
     </row>
     <row r="999" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B999" s="5"/>
+      <c r="B999" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
